--- a/Results/Phase 2/Carbon dioxide/carbon dioxide particulate matter results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide particulate matter results.xlsx
@@ -2981,7 +2981,7 @@
         <v>2.981321355122826e-08</v>
       </c>
       <c r="O12" t="n">
-        <v>2.974097462118772e-08</v>
+        <v>2.974097462118771e-08</v>
       </c>
       <c r="P12" t="n">
         <v>3.05179575966664e-08</v>
@@ -5014,85 +5014,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.458853221863536e-09</v>
+        <v>4.458853221863291e-09</v>
       </c>
       <c r="C2" t="n">
         <v>5.316474615628572e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.030864505352295e-08</v>
+        <v>1.030864505352275e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>5.32610341725782e-09</v>
+        <v>5.326103417257815e-09</v>
       </c>
       <c r="F2" t="n">
         <v>9.001546257668835e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>4.193936102380602e-08</v>
+        <v>4.193936102380582e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>4.425626905016978e-09</v>
+        <v>4.4256269050168e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>1.032996693433084e-08</v>
+        <v>1.032996693433064e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.07118679634643e-08</v>
+        <v>2.071186796346396e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>9.770296104459573e-09</v>
+        <v>9.77029610445937e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>5.720908491437825e-08</v>
+        <v>5.720908491437804e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.376877902219157e-08</v>
+        <v>1.376877902219155e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>7.346435634956617e-09</v>
+        <v>7.346435634956435e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>5.758675434486632e-09</v>
+        <v>5.758675434486467e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>8.679318692443753e-09</v>
+        <v>8.679318692443601e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.342235463032716e-09</v>
+        <v>7.342235463032527e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>4.192211064420229e-09</v>
+        <v>4.19221106442004e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>7.334929551110736e-09</v>
+        <v>7.334929551110573e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>6.75594148128099e-09</v>
+        <v>6.755941481280786e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>9.279525412314413e-09</v>
+        <v>9.279525412314076e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>5.165030558069319e-09</v>
+        <v>5.165030558069289e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.568582545374827e-08</v>
+        <v>1.568582545374808e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.288874823190039e-08</v>
+        <v>3.288874823190017e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.496593303772779e-08</v>
+        <v>1.496593303772762e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.441411253745581e-09</v>
+        <v>9.441411253745364e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.209925434411912e-09</v>
+        <v>9.2099254344117e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.636567450922116e-08</v>
+        <v>1.636567450922114e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5102,85 +5102,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.56949057128668e-09</v>
+        <v>3.569490571286469e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>4.858130990869393e-09</v>
+        <v>4.858130990869402e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.874077219907313e-09</v>
+        <v>4.874077219907301e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.060105001133955e-09</v>
+        <v>4.060105001133962e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.702375646972773e-09</v>
+        <v>3.702375646972776e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.144591760097623e-09</v>
+        <v>5.144591760097691e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.874077219907313e-09</v>
+        <v>4.874077219907301e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.874077219907313e-09</v>
+        <v>4.874077219907301e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.817602115734182e-09</v>
+        <v>4.817602115734076e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.874077219907313e-09</v>
+        <v>4.874077219907301e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.874077219907313e-09</v>
+        <v>4.874077219907301e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.80634506135421e-09</v>
+        <v>4.806345061354219e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.862804314578586e-09</v>
+        <v>3.862804314578442e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.140710889662282e-09</v>
+        <v>4.140710889662264e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>4.072589272948789e-09</v>
+        <v>4.072589272948825e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.313109519060411e-09</v>
+        <v>3.313109519060149e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.874077219907313e-09</v>
+        <v>4.874077219907301e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.874077219907313e-09</v>
+        <v>4.874077219907301e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.874077219907313e-09</v>
+        <v>4.874077219907301e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.236764720162504e-09</v>
+        <v>4.236764720162425e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.385393555121909e-09</v>
+        <v>4.385393555121872e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.874333608461551e-09</v>
+        <v>4.87433360846135e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.432677477619592e-09</v>
+        <v>3.432677477619428e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.170238034134062e-09</v>
+        <v>6.170238034133982e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.545257204471016e-09</v>
+        <v>3.545257204470963e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.874077219907313e-09</v>
+        <v>4.874077219907301e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.189510614061285e-09</v>
+        <v>6.189510614061289e-09</v>
       </c>
     </row>
     <row r="4">
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.553638257514463e-08</v>
+        <v>3.55363825751442e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.583884148666962e-08</v>
+        <v>3.583884148666936e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.766856300606068e-08</v>
+        <v>3.766856300606015e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.577665689968091e-08</v>
+        <v>3.577665689968083e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.71474298744662e-08</v>
+        <v>3.714742987446587e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.919758755060951e-08</v>
+        <v>4.919758755060899e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.552427197281709e-08</v>
+        <v>3.552427197281676e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.767633458124099e-08</v>
+        <v>3.767633458124048e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.941828118715883e-08</v>
+        <v>3.941828118715836e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.747234113573962e-08</v>
+        <v>3.74723411357392e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.476322260257241e-08</v>
+        <v>5.47632226025718e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>3.888669662458458e-08</v>
+        <v>3.888669662458405e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.658887245701239e-08</v>
+        <v>3.658887245701198e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.601015250836265e-08</v>
+        <v>3.60101525083623e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.707469267996342e-08</v>
+        <v>3.707469267996289e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.658734154366712e-08</v>
+        <v>3.658734154366658e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.543919463982681e-08</v>
+        <v>3.543919463982631e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.65846786245618e-08</v>
+        <v>3.658467862456118e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.637364427193016e-08</v>
+        <v>3.63736442719296e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.72934609813733e-08</v>
+        <v>3.729346098137289e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.232505679447679e-08</v>
+        <v>2.232505679447687e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.962848211990264e-08</v>
+        <v>3.962848211990215e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>4.589874546562091e-08</v>
+        <v>4.589874546562064e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.936608978766676e-08</v>
+        <v>3.93660897876663e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.735246646961528e-08</v>
+        <v>3.735246646961471e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.726809260671188e-08</v>
+        <v>3.726809260671137e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.984620895905684e-08</v>
+        <v>3.984620895905622e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.521222033243253e-08</v>
+        <v>3.521222033243229e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.567178061758749e-08</v>
+        <v>3.567178061758715e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.568772684662529e-08</v>
+        <v>3.568772684662485e-08</v>
       </c>
       <c r="E5" t="n">
         <v>3.531521534310772e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.52159444128708e-08</v>
+        <v>3.521594441287007e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.578632621998238e-08</v>
+        <v>3.57863262199822e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.568772684662529e-08</v>
+        <v>3.568772684662485e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.568772684662529e-08</v>
+        <v>3.568772684662485e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.36250079255534e-08</v>
+        <v>3.362500792555328e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.568772684662529e-08</v>
+        <v>3.568772684662484e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.568772684662529e-08</v>
+        <v>3.568772684662485e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.561999468807247e-08</v>
+        <v>3.5619994688072e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.531912974759909e-08</v>
+        <v>3.53191297475985e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.54204234308734e-08</v>
+        <v>3.542042343087284e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.539559390150562e-08</v>
+        <v>3.539559390150505e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.511877244947459e-08</v>
+        <v>3.511877244947409e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.568772684662529e-08</v>
+        <v>3.568772684662485e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.568772684662529e-08</v>
+        <v>3.568772684662484e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.568772684662529e-08</v>
+        <v>3.568772684662484e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.545543392416932e-08</v>
+        <v>3.545543392416927e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.204088826186244e-08</v>
+        <v>2.204088826186268e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.568782029724267e-08</v>
+        <v>3.568782029724206e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.516235356633181e-08</v>
+        <v>3.516235356633118e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.616016224312195e-08</v>
+        <v>3.616016224312168e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.52033875547915e-08</v>
+        <v>3.520338755479069e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.568772684662529e-08</v>
+        <v>3.568772684662485e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.613711671382011e-08</v>
+        <v>3.613711671382006e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5366,82 +5366,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.705306016132882e-09</v>
+        <v>2.70530601613274e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>3.007764927657655e-09</v>
+        <v>3.007764927657658e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>4.837486447048957e-09</v>
+        <v>4.837486447048831e-09</v>
       </c>
       <c r="E6" t="n">
         <v>2.945580340669325e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.316353315454371e-09</v>
+        <v>4.316353315454373e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.625001796490437e-08</v>
+        <v>1.625001796490414e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.693195413805424e-09</v>
+        <v>2.693195413805288e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.845258022229272e-09</v>
+        <v>4.845258022229128e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.481315136936196e-09</v>
+        <v>8.481315136936095e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.641264576727879e-09</v>
+        <v>4.641264576727747e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>2.193214604356064e-08</v>
+        <v>2.193214604356048e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.055620065572659e-09</v>
+        <v>6.055620065572647e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.757795898000689e-09</v>
+        <v>3.757795898000561e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.062582922657579e-09</v>
+        <v>3.062582922657429e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>4.127123094258284e-09</v>
+        <v>4.127123094258148e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.756264984655337e-09</v>
+        <v>3.756264984655192e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>2.608118080815091e-09</v>
+        <v>2.60811808081495e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.753602065550131e-09</v>
+        <v>3.753602065549994e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>3.542567712918357e-09</v>
+        <v>3.542567712918224e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.345891395668001e-09</v>
+        <v>4.34589139566787e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>2.76905792167006e-09</v>
+        <v>2.769057921670074e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>6.680912534197517e-09</v>
+        <v>6.680912534197373e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.295117587991581e-08</v>
+        <v>1.295117587991566e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.535013228655004e-09</v>
+        <v>6.535013228654857e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.521389910603526e-09</v>
+        <v>4.521389910603377e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.437016047700135e-09</v>
+        <v>4.437016047699997e-09</v>
       </c>
       <c r="AB6" t="n">
         <v>7.015132400044773e-09</v>
@@ -5454,85 +5454,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.381143773421128e-09</v>
+        <v>2.381143773420984e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.84070405857551e-09</v>
+        <v>2.840704058575514e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8566502876134e-09</v>
+        <v>2.856650287613392e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.484138784096138e-09</v>
+        <v>2.48413878409614e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.384867853858629e-09</v>
+        <v>2.38486785385863e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.838756634277252e-09</v>
+        <v>2.838756634277329e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8566502876134e-09</v>
+        <v>2.856650287613392e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8566502876134e-09</v>
+        <v>2.856650287613392e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.688041875331323e-09</v>
+        <v>2.688041875331136e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8566502876134e-09</v>
+        <v>2.856650287613393e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.8566502876134e-09</v>
+        <v>2.856650287613392e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.788918129060459e-09</v>
+        <v>2.78891812906046e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.488053188587182e-09</v>
+        <v>2.488053188586998e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.472853845168094e-09</v>
+        <v>2.472853845167934e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.448024315800472e-09</v>
+        <v>2.448024315800295e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.287695890462817e-09</v>
+        <v>2.287695890462816e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8566502876134e-09</v>
+        <v>2.856650287613392e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8566502876134e-09</v>
+        <v>2.856650287613393e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8566502876134e-09</v>
+        <v>2.856650287613393e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.507864338464251e-09</v>
+        <v>2.50786433846423e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.484889389055634e-09</v>
+        <v>2.484889389055628e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.740250711537385e-09</v>
+        <v>2.740250711537316e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.214783980626658e-09</v>
+        <v>2.214783980626421e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.329085684110198e-09</v>
+        <v>3.32908568411032e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.37231099577948e-09</v>
+        <v>2.372310995779257e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.8566502876134e-09</v>
+        <v>2.856650287613392e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.306040154808487e-09</v>
+        <v>3.30604015480849e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>3.411633494257712e-09</v>
+        <v>3.41163349425772e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.13019851510712e-09</v>
+        <v>4.130198515107125e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5630,85 +5630,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.923867437566498e-09</v>
+        <v>4.923867437566463e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>5.862693173625907e-09</v>
+        <v>5.862693173625909e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.121065620902918e-08</v>
+        <v>1.121065620902923e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>5.98413556136751e-09</v>
+        <v>5.984135561367507e-09</v>
       </c>
       <c r="F9" t="n">
         <v>9.881523177041566e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>4.52042812332707e-08</v>
+        <v>4.520428123327075e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.888159015509925e-09</v>
+        <v>4.888159015509929e-09</v>
       </c>
       <c r="I9" t="n">
         <v>1.123357089808258e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.245172493768719e-08</v>
+        <v>2.245172493768717e-08</v>
       </c>
       <c r="K9" t="n">
         <v>1.063209098389018e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.161469915259588e-08</v>
+        <v>6.161469915259578e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>1.500206448373172e-08</v>
+        <v>1.50020644837317e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.027160890345167e-09</v>
+        <v>8.027160890345159e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>6.320790255741145e-09</v>
+        <v>6.320790255741151e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>9.45961429734203e-09</v>
+        <v>9.45961429734204e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.022646953020648e-09</v>
+        <v>8.022646953020641e-09</v>
       </c>
       <c r="R9" t="n">
         <v>4.637306313743117e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>8.01479526763457e-09</v>
+        <v>8.014795267634572e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>7.392555057903213e-09</v>
+        <v>7.392555057903208e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.010465825371285e-08</v>
+        <v>1.01046582537129e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>5.824123398462347e-09</v>
+        <v>5.824123398462381e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.698952806209411e-08</v>
+        <v>1.698952806209409e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.547756060586874e-08</v>
+        <v>3.547756060586873e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.621585753022929e-08</v>
+        <v>1.621585753022927e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.027863745151269e-08</v>
+        <v>1.027863745151266e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.002985894936779e-08</v>
+        <v>1.002985894936777e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.777101500288015e-08</v>
+        <v>1.777101500288013e-08</v>
       </c>
     </row>
     <row r="10">
@@ -5718,85 +5718,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.968066737933939e-09</v>
+        <v>3.968066737933943e-09</v>
       </c>
       <c r="C10" t="n">
-        <v>5.370109909720233e-09</v>
+        <v>5.37010990972024e-09</v>
       </c>
       <c r="D10" t="n">
-        <v>5.370109909720233e-09</v>
+        <v>5.37010990972024e-09</v>
       </c>
       <c r="E10" t="n">
-        <v>4.62356327841855e-09</v>
+        <v>4.623563278418553e-09</v>
       </c>
       <c r="F10" t="n">
-        <v>4.186488678020989e-09</v>
+        <v>4.186488678020999e-09</v>
       </c>
       <c r="G10" t="n">
-        <v>5.660832694859767e-09</v>
+        <v>5.660832694859773e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>5.370109909720233e-09</v>
+        <v>5.37010990972024e-09</v>
       </c>
       <c r="I10" t="n">
-        <v>5.370109909720233e-09</v>
+        <v>5.37010990972024e-09</v>
       </c>
       <c r="J10" t="n">
-        <v>5.370109909720233e-09</v>
+        <v>5.37010990972024e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>5.370109909720233e-09</v>
+        <v>5.37010990972024e-09</v>
       </c>
       <c r="L10" t="n">
-        <v>5.370109909720233e-09</v>
+        <v>5.37010990972024e-09</v>
       </c>
       <c r="M10" t="n">
-        <v>5.370109909720016e-09</v>
+        <v>5.370109909720021e-09</v>
       </c>
       <c r="N10" t="n">
-        <v>4.283291894812835e-09</v>
+        <v>4.283291894812843e-09</v>
       </c>
       <c r="O10" t="n">
         <v>4.581958921953335e-09</v>
       </c>
       <c r="P10" t="n">
-        <v>4.508748416798238e-09</v>
+        <v>4.508748416798249e-09</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.69253325456638e-09</v>
+        <v>3.692533254566384e-09</v>
       </c>
       <c r="R10" t="n">
-        <v>5.370109909720233e-09</v>
+        <v>5.37010990972024e-09</v>
       </c>
       <c r="S10" t="n">
-        <v>5.370109909720233e-09</v>
+        <v>5.37010990972024e-09</v>
       </c>
       <c r="T10" t="n">
-        <v>5.370109909720233e-09</v>
+        <v>5.37010990972024e-09</v>
       </c>
       <c r="U10" t="n">
-        <v>4.685188260778043e-09</v>
+        <v>4.685188260778052e-09</v>
       </c>
       <c r="V10" t="n">
-        <v>4.986245180399991e-09</v>
+        <v>4.986245180399996e-09</v>
       </c>
       <c r="W10" t="n">
-        <v>5.370385451265858e-09</v>
+        <v>5.370385451265863e-09</v>
       </c>
       <c r="X10" t="n">
-        <v>3.821033297119837e-09</v>
+        <v>3.821033297119841e-09</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.763097812091226e-09</v>
+        <v>6.76309781209123e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.942023066163264e-09</v>
+        <v>3.942023066163269e-09</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.370109909720233e-09</v>
+        <v>5.37010990972024e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.834661239586125e-09</v>
+        <v>6.834661239586134e-09</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="C11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="D11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="E11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="F11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="G11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="I11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="J11" t="n">
-        <v>2.953136004299697e-08</v>
+        <v>2.953136004299628e-08</v>
       </c>
       <c r="K11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="L11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="M11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="O11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="P11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="R11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="S11" t="n">
-        <v>3.090328188426283e-08</v>
+        <v>3.090328188426243e-08</v>
       </c>
       <c r="T11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="U11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="V11" t="n">
-        <v>1.9746952562338e-08</v>
+        <v>1.974695256233777e-08</v>
       </c>
       <c r="W11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="X11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.12564748677488e-08</v>
+        <v>3.125647486774806e-08</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.16465833290431e-08</v>
+        <v>3.164658332904294e-08</v>
       </c>
       <c r="C12" t="n">
-        <v>3.210804005609097e-08</v>
+        <v>3.210804005609055e-08</v>
       </c>
       <c r="D12" t="n">
-        <v>3.473669990626549e-08</v>
+        <v>3.473669990626512e-08</v>
       </c>
       <c r="E12" t="n">
-        <v>3.21677320783904e-08</v>
+        <v>3.216773207838986e-08</v>
       </c>
       <c r="F12" t="n">
-        <v>3.408339721632554e-08</v>
+        <v>3.408339721632558e-08</v>
       </c>
       <c r="G12" t="n">
-        <v>5.144543118798353e-08</v>
+        <v>5.144543118798334e-08</v>
       </c>
       <c r="H12" t="n">
-        <v>3.162903173140641e-08</v>
+        <v>3.162903173140586e-08</v>
       </c>
       <c r="I12" t="n">
-        <v>3.47479630587397e-08</v>
+        <v>3.474796305873934e-08</v>
       </c>
       <c r="J12" t="n">
-        <v>3.85368562631695e-08</v>
+        <v>3.853685626316912e-08</v>
       </c>
       <c r="K12" t="n">
-        <v>3.445232038307847e-08</v>
+        <v>3.445232038307821e-08</v>
       </c>
       <c r="L12" t="n">
-        <v>5.951156897232283e-08</v>
+        <v>5.951156897232257e-08</v>
       </c>
       <c r="M12" t="n">
-        <v>3.660027350267106e-08</v>
+        <v>3.660027350267049e-08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.317193098919451e-08</v>
+        <v>3.317193098919421e-08</v>
       </c>
       <c r="O12" t="n">
-        <v>3.23332064230361e-08</v>
+        <v>3.233320642303567e-08</v>
       </c>
       <c r="P12" t="n">
-        <v>3.387601827126663e-08</v>
+        <v>3.387601827126614e-08</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.316971227419348e-08</v>
+        <v>3.31697122741933e-08</v>
       </c>
       <c r="R12" t="n">
-        <v>3.150573124838577e-08</v>
+        <v>3.150573124838537e-08</v>
       </c>
       <c r="S12" t="n">
-        <v>3.316585297112932e-08</v>
+        <v>3.316585297112906e-08</v>
       </c>
       <c r="T12" t="n">
-        <v>3.286000608220032e-08</v>
+        <v>3.286000608219991e-08</v>
       </c>
       <c r="U12" t="n">
-        <v>3.419307378165151e-08</v>
+        <v>3.41930737816511e-08</v>
       </c>
       <c r="V12" t="n">
-        <v>2.057955972521671e-08</v>
+        <v>2.057955972521683e-08</v>
       </c>
       <c r="W12" t="n">
-        <v>3.757716239990927e-08</v>
+        <v>3.757716239990888e-08</v>
       </c>
       <c r="X12" t="n">
-        <v>4.666450061350948e-08</v>
+        <v>4.666450061350914e-08</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.719688365622434e-08</v>
+        <v>3.719688365622396e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.427858898229794e-08</v>
+        <v>3.427858898229764e-08</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.415630802114582e-08</v>
+        <v>3.415630802114555e-08</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.796128310737876e-08</v>
+        <v>3.796128310737845e-08</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.117678297566357e-08</v>
+        <v>3.117678297566303e-08</v>
       </c>
       <c r="C13" t="n">
-        <v>3.186592285368599e-08</v>
+        <v>3.186592285368536e-08</v>
       </c>
       <c r="D13" t="n">
-        <v>3.186592285368599e-08</v>
+        <v>3.186592285368536e-08</v>
       </c>
       <c r="E13" t="n">
-        <v>3.149897619698808e-08</v>
+        <v>3.14989761969877e-08</v>
       </c>
       <c r="F13" t="n">
-        <v>3.128414291448563e-08</v>
+        <v>3.128414291448552e-08</v>
       </c>
       <c r="G13" t="n">
-        <v>3.200882049672654e-08</v>
+        <v>3.200882049672615e-08</v>
       </c>
       <c r="H13" t="n">
-        <v>3.186592285368599e-08</v>
+        <v>3.186592285368536e-08</v>
       </c>
       <c r="I13" t="n">
-        <v>3.186592285368599e-08</v>
+        <v>3.186592285368536e-08</v>
       </c>
       <c r="J13" t="n">
-        <v>3.014080802893409e-08</v>
+        <v>3.014080802893371e-08</v>
       </c>
       <c r="K13" t="n">
-        <v>3.186592285368599e-08</v>
+        <v>3.186592285368536e-08</v>
       </c>
       <c r="L13" t="n">
-        <v>3.186592285368599e-08</v>
+        <v>3.186592285368536e-08</v>
       </c>
       <c r="M13" t="n">
-        <v>3.186592285368588e-08</v>
+        <v>3.186592285368526e-08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.133172415759899e-08</v>
+        <v>3.133172415759855e-08</v>
       </c>
       <c r="O13" t="n">
-        <v>3.147852659763424e-08</v>
+        <v>3.147852659763408e-08</v>
       </c>
       <c r="P13" t="n">
-        <v>3.144254177233934e-08</v>
+        <v>3.144254177233883e-08</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.104135126076342e-08</v>
+        <v>3.104135126076334e-08</v>
       </c>
       <c r="R13" t="n">
-        <v>3.186592285368599e-08</v>
+        <v>3.186592285368536e-08</v>
       </c>
       <c r="S13" t="n">
-        <v>3.186592285368599e-08</v>
+        <v>3.186592285368536e-08</v>
       </c>
       <c r="T13" t="n">
-        <v>3.186592285368599e-08</v>
+        <v>3.186592285368536e-08</v>
       </c>
       <c r="U13" t="n">
-        <v>3.152926644316635e-08</v>
+        <v>3.152926644316636e-08</v>
       </c>
       <c r="V13" t="n">
-        <v>2.016772127072927e-08</v>
+        <v>2.016772127072902e-08</v>
       </c>
       <c r="W13" t="n">
-        <v>3.186605828936367e-08</v>
+        <v>3.186605828936331e-08</v>
       </c>
       <c r="X13" t="n">
-        <v>3.110451229990509e-08</v>
+        <v>3.110451229990456e-08</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.255061183648204e-08</v>
+        <v>3.255061183648198e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.116398184860218e-08</v>
+        <v>3.116398184860189e-08</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.186592285368599e-08</v>
+        <v>3.186592285368536e-08</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.258578708121564e-08</v>
+        <v>3.25857870812155e-08</v>
       </c>
     </row>
     <row r="14">
@@ -6070,85 +6070,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="C14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="D14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="E14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="F14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>2.925762612826218e-09</v>
+        <v>2.925762612826222e-09</v>
       </c>
       <c r="H14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="I14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="J14" t="n">
-        <v>2.929511415366745e-09</v>
+        <v>2.929511415366748e-09</v>
       </c>
       <c r="K14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="L14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="M14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="O14" t="n">
-        <v>2.925762612826218e-09</v>
+        <v>2.925762612826222e-09</v>
       </c>
       <c r="P14" t="n">
-        <v>2.925762612826218e-09</v>
+        <v>2.925762612826222e-09</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="R14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="S14" t="n">
-        <v>2.672738790843064e-09</v>
+        <v>2.672738790843069e-09</v>
       </c>
       <c r="T14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="U14" t="n">
-        <v>2.925762612826218e-09</v>
+        <v>2.925762612826222e-09</v>
       </c>
       <c r="V14" t="n">
-        <v>2.931285006610288e-09</v>
+        <v>2.931285006610289e-09</v>
       </c>
       <c r="W14" t="n">
-        <v>2.925762612826218e-09</v>
+        <v>2.925762612826222e-09</v>
       </c>
       <c r="X14" t="n">
-        <v>2.925762612826218e-09</v>
+        <v>2.925762612826222e-09</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.025931774329027e-09</v>
+        <v>3.025931774329032e-09</v>
       </c>
     </row>
     <row r="15">
@@ -6158,85 +6158,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.416040235623389e-09</v>
+        <v>3.416040235623384e-09</v>
       </c>
       <c r="C15" t="n">
-        <v>3.877496962671218e-09</v>
+        <v>3.877496962671223e-09</v>
       </c>
       <c r="D15" t="n">
-        <v>6.50615681284583e-09</v>
+        <v>6.506156812845818e-09</v>
       </c>
       <c r="E15" t="n">
-        <v>3.937188984970629e-09</v>
+        <v>3.937188984970633e-09</v>
       </c>
       <c r="F15" t="n">
         <v>5.852854122906192e-09</v>
       </c>
       <c r="G15" t="n">
-        <v>2.311471893306113e-08</v>
+        <v>2.311471893306105e-08</v>
       </c>
       <c r="H15" t="n">
-        <v>3.398488637986714e-09</v>
+        <v>3.39848863798672e-09</v>
       </c>
       <c r="I15" t="n">
-        <v>6.51741996531998e-09</v>
+        <v>6.517419965319979e-09</v>
       </c>
       <c r="J15" t="n">
-        <v>1.193500763553984e-08</v>
+        <v>1.193500763553979e-08</v>
       </c>
       <c r="K15" t="n">
-        <v>6.221777289658752e-09</v>
+        <v>6.221777289658746e-09</v>
       </c>
       <c r="L15" t="n">
-        <v>3.12810258789031e-08</v>
+        <v>3.128102587890307e-08</v>
       </c>
       <c r="M15" t="n">
-        <v>8.36973040925136e-09</v>
+        <v>8.369730409251358e-09</v>
       </c>
       <c r="N15" t="n">
-        <v>4.941387895774868e-09</v>
+        <v>4.941387895774866e-09</v>
       </c>
       <c r="O15" t="n">
-        <v>4.002494168113519e-09</v>
+        <v>4.002494168113539e-09</v>
       </c>
       <c r="P15" t="n">
-        <v>5.54530601634404e-09</v>
+        <v>5.545306016344043e-09</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.939169180773933e-09</v>
+        <v>4.939169180773929e-09</v>
       </c>
       <c r="R15" t="n">
-        <v>3.275188154965988e-09</v>
+        <v>3.275188154965987e-09</v>
       </c>
       <c r="S15" t="n">
-        <v>4.935309877709572e-09</v>
+        <v>4.935309877709573e-09</v>
       </c>
       <c r="T15" t="n">
         <v>4.629462988780633e-09</v>
       </c>
       <c r="U15" t="n">
-        <v>5.862361526729014e-09</v>
+        <v>5.86236152672896e-09</v>
       </c>
       <c r="V15" t="n">
-        <v>3.763892169489045e-09</v>
+        <v>3.763892169489037e-09</v>
       </c>
       <c r="W15" t="n">
-        <v>9.246450144986712e-09</v>
+        <v>9.246450144986716e-09</v>
       </c>
       <c r="X15" t="n">
         <v>1.833378835858696e-08</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.966340562804657e-09</v>
+        <v>8.966340562804669e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.048045888878217e-09</v>
+        <v>6.048045888878203e-09</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.925764927726148e-09</v>
+        <v>5.925764927726139e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.730740013959061e-09</v>
+        <v>9.730740013959064e-09</v>
       </c>
     </row>
     <row r="16">
@@ -6246,85 +6246,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9462398822439e-09</v>
+        <v>2.946239882243905e-09</v>
       </c>
       <c r="C16" t="n">
-        <v>3.635379760266296e-09</v>
+        <v>3.635379760266299e-09</v>
       </c>
       <c r="D16" t="n">
-        <v>3.635379760266296e-09</v>
+        <v>3.635379760266299e-09</v>
       </c>
       <c r="E16" t="n">
-        <v>3.268433103568272e-09</v>
+        <v>3.268433103568275e-09</v>
       </c>
       <c r="F16" t="n">
-        <v>3.053599821066063e-09</v>
+        <v>3.053599821066066e-09</v>
       </c>
       <c r="G16" t="n">
-        <v>3.678108241804062e-09</v>
+        <v>3.678108241804064e-09</v>
       </c>
       <c r="H16" t="n">
-        <v>3.635379760266296e-09</v>
+        <v>3.635379760266299e-09</v>
       </c>
       <c r="I16" t="n">
-        <v>3.635379760266296e-09</v>
+        <v>3.635379760266299e-09</v>
       </c>
       <c r="J16" t="n">
-        <v>3.538959401304016e-09</v>
+        <v>3.53895940130402e-09</v>
       </c>
       <c r="K16" t="n">
-        <v>3.635379760266296e-09</v>
+        <v>3.635379760266299e-09</v>
       </c>
       <c r="L16" t="n">
-        <v>3.635379760266296e-09</v>
+        <v>3.635379760266299e-09</v>
       </c>
       <c r="M16" t="n">
-        <v>3.635379760266188e-09</v>
+        <v>3.635379760266193e-09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.101181064179362e-09</v>
+        <v>3.101181064179368e-09</v>
       </c>
       <c r="O16" t="n">
-        <v>3.147814342711751e-09</v>
+        <v>3.147814342711757e-09</v>
       </c>
       <c r="P16" t="n">
-        <v>3.111829517416922e-09</v>
+        <v>3.111829517416926e-09</v>
       </c>
       <c r="Q16" t="n">
         <v>2.810808167343794e-09</v>
       </c>
       <c r="R16" t="n">
-        <v>3.635379760266296e-09</v>
+        <v>3.635379760266299e-09</v>
       </c>
       <c r="S16" t="n">
-        <v>3.635379760266296e-09</v>
+        <v>3.635379760266299e-09</v>
       </c>
       <c r="T16" t="n">
-        <v>3.635379760266296e-09</v>
+        <v>3.635379760266299e-09</v>
       </c>
       <c r="U16" t="n">
-        <v>3.198554188244012e-09</v>
+        <v>3.198554188244015e-09</v>
       </c>
       <c r="V16" t="n">
-        <v>3.352053715001617e-09</v>
+        <v>3.352053715001619e-09</v>
       </c>
       <c r="W16" t="n">
-        <v>3.535346034441196e-09</v>
+        <v>3.535346034441197e-09</v>
       </c>
       <c r="X16" t="n">
-        <v>2.773800044982409e-09</v>
+        <v>2.773800044982413e-09</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.320068743062423e-09</v>
+        <v>4.320068743062429e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.933438755182718e-09</v>
+        <v>2.933438755182721e-09</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.635379760266296e-09</v>
+        <v>3.635379760266299e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.355243987796054e-09</v>
+        <v>4.355243987796061e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.077919370254182e-09</v>
+        <v>4.077919370254153e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>4.477668525083476e-09</v>
+        <v>4.477668525083472e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.179031957221329e-09</v>
+        <v>6.179031957221147e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>4.272924230147872e-09</v>
+        <v>4.272924230147879e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>9.032803863534491e-09</v>
+        <v>9.032803863534447e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>3.631402543672503e-08</v>
+        <v>3.631402543672477e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>4.469466262815039e-09</v>
+        <v>4.469466262815004e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>8.462642942309077e-09</v>
+        <v>8.462642942309014e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.734803353821478e-08</v>
+        <v>1.734803353821465e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.014878352143081e-08</v>
+        <v>1.01487835214308e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>4.554795192339025e-08</v>
+        <v>4.554795192339011e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.171391244872189e-08</v>
+        <v>1.171391244872185e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.926182002557555e-09</v>
+        <v>3.926182002557502e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>5.890409793387678e-09</v>
+        <v>5.890409793387628e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>6.718063717287386e-09</v>
+        <v>6.718063717287401e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.80432737952297e-09</v>
+        <v>6.804327379522913e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>5.683243015155382e-09</v>
+        <v>5.6832430151553e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>7.408936946010025e-09</v>
+        <v>7.40893694601001e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>7.454086110988502e-09</v>
+        <v>7.454086110988432e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.013952201669834e-08</v>
+        <v>1.013952201669824e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>5.655411115377075e-09</v>
+        <v>5.655411115376966e-09</v>
       </c>
       <c r="W2" t="n">
         <v>1.07428130109584e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.549204168525471e-08</v>
+        <v>3.549204168525462e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.035381213114138e-08</v>
+        <v>2.035381213114126e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.421370149017342e-09</v>
+        <v>8.421370149017294e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.300506880142884e-09</v>
+        <v>9.30050688014282e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.45034746235814e-08</v>
+        <v>1.450347462358137e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6578,85 +6578,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.488308750213283e-09</v>
+        <v>3.488308750213156e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>4.75941286417805e-09</v>
+        <v>4.759412864178045e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.771002256236989e-09</v>
+        <v>4.771002256236948e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.975459998530396e-09</v>
+        <v>3.975459998530388e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.626047664983365e-09</v>
+        <v>3.62604766498336e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.036977110689627e-09</v>
+        <v>5.036977110689691e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.771002256236989e-09</v>
+        <v>4.771002256236948e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.771002256236989e-09</v>
+        <v>4.771002256236948e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.718876804675214e-09</v>
+        <v>4.718876804675233e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.771002256236989e-09</v>
+        <v>4.771002256236948e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.771002256236989e-09</v>
+        <v>4.771002256236948e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.705117883859011e-09</v>
+        <v>4.705117883859002e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.776700199064568e-09</v>
+        <v>3.776700199064444e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.049943037721876e-09</v>
+        <v>4.049943037721831e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.982964615497959e-09</v>
+        <v>3.982964615497953e-09</v>
       </c>
       <c r="Q3" t="n">
         <v>3.236230200192287e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.771002256236989e-09</v>
+        <v>4.771002256236948e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.771002256236989e-09</v>
+        <v>4.771002256236948e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.771002256236989e-09</v>
+        <v>4.771002256236948e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.144446411453025e-09</v>
+        <v>4.144446411453028e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.298972049466928e-09</v>
+        <v>4.298972049466858e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.771254342165371e-09</v>
+        <v>4.771254342165324e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.353791608732861e-09</v>
+        <v>3.353791608732767e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.045516513663493e-09</v>
+        <v>6.0455165136635e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.464482059760723e-09</v>
+        <v>3.464482059760786e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.771002256236989e-09</v>
+        <v>4.771002256236948e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.06582726885343e-09</v>
+        <v>6.065827268853421e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.499340540176751e-08</v>
+        <v>3.499340540176795e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.513174407986826e-08</v>
+        <v>3.513174407986857e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.575923626720739e-08</v>
+        <v>3.575923626720733e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.499295820405918e-08</v>
+        <v>3.499295820405954e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.675994385607356e-08</v>
+        <v>3.675994385607375e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.674308752752728e-08</v>
+        <v>4.674308752752723e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.513611964633024e-08</v>
+        <v>3.51361196463304e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.659158565575785e-08</v>
+        <v>3.659158565575802e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.794726463155272e-08</v>
+        <v>3.794726463155298e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.720616409718538e-08</v>
+        <v>3.720616409718554e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.010874530167761e-08</v>
+        <v>5.01087453016776e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>3.773476492021173e-08</v>
+        <v>3.773476492021193e-08</v>
       </c>
       <c r="N4" t="n">
         <v>3.493809891303228e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.565403687766264e-08</v>
+        <v>3.565403687766255e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.595570701412098e-08</v>
+        <v>3.595570701412092e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.598714910604682e-08</v>
+        <v>3.598714910604684e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.557852701967208e-08</v>
+        <v>3.557852701967222e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.620752219334734e-08</v>
+        <v>3.620752219334732e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.622397853381372e-08</v>
+        <v>3.622397853381376e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.720278838746446e-08</v>
+        <v>3.720278838746444e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.315004659789075e-08</v>
+        <v>2.31500465978907e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.742268087067175e-08</v>
+        <v>3.742268087067211e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>4.644348410233693e-08</v>
+        <v>4.644348410233688e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.092577719192884e-08</v>
+        <v>4.092577719192883e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.657654220725265e-08</v>
+        <v>3.657654220725256e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.689697722240314e-08</v>
+        <v>3.689697722240353e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.876476449837114e-08</v>
+        <v>3.876476449837103e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6757,82 +6757,82 @@
         <v>3.477849925432011e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.52344365830592e-08</v>
+        <v>3.52344365830594e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.524602597511813e-08</v>
+        <v>3.524602597511835e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4884535984636e-08</v>
+        <v>3.488453598463627e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.478924471103841e-08</v>
+        <v>3.478924471103876e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.534297068633166e-08</v>
+        <v>3.534297068633192e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.524602597511813e-08</v>
+        <v>3.524602597511835e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.524602597511813e-08</v>
+        <v>3.524602597511835e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.334408530122322e-08</v>
+        <v>3.334408530122333e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.524602597511813e-08</v>
+        <v>3.524602597511835e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.524602597511813e-08</v>
+        <v>3.524602597511835e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.518014160274018e-08</v>
+        <v>3.518014160274051e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.488361455096304e-08</v>
+        <v>3.488361455096315e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.498320835707418e-08</v>
+        <v>3.498320835707431e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.495879550867393e-08</v>
+        <v>3.4958795508674e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.468661958289323e-08</v>
+        <v>3.468661958289364e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.524602597511813e-08</v>
+        <v>3.524602597511835e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.524602597511813e-08</v>
+        <v>3.524602597511835e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.524602597511813e-08</v>
+        <v>3.524602597511835e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.501765372708454e-08</v>
+        <v>3.501765372708489e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.265564048647815e-08</v>
+        <v>2.265564048647816e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.524611785747888e-08</v>
+        <v>3.524611785747926e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.47294693358305e-08</v>
+        <v>3.472946933583053e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.571057145584805e-08</v>
+        <v>3.571057145584838e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.476981470543729e-08</v>
+        <v>3.476981470543715e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.524602597511813e-08</v>
+        <v>3.524602597511835e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.568934111743032e-08</v>
+        <v>3.568934111743024e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.536009981360452e-09</v>
+        <v>2.536009981360401e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>2.674348659461184e-09</v>
+        <v>2.674348659461183e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>3.301840846800304e-09</v>
+        <v>3.301840846800214e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>2.535562783652089e-09</v>
+        <v>2.53556278365209e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.302548435666492e-09</v>
+        <v>4.302548435666468e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.416995459017135e-08</v>
+        <v>1.416995459017121e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.678724225923137e-09</v>
+        <v>2.678724225923107e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.134190235350756e-09</v>
+        <v>4.134190235350657e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.228274372972879e-09</v>
+        <v>7.2282743729729e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.748768676778277e-09</v>
+        <v>4.748768676778309e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.765134988127045e-08</v>
+        <v>1.765134988127031e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.277369499804626e-09</v>
+        <v>5.277369499804599e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.480703492625178e-09</v>
+        <v>2.480703492625075e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.080903940306706e-09</v>
+        <v>3.080903940306615e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>3.382574076765078e-09</v>
+        <v>3.382574076764941e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5297536856397e-09</v>
+        <v>3.529753685639599e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>3.121131599264974e-09</v>
+        <v>3.121131599264881e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.750126772940265e-09</v>
+        <v>3.750126772940175e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>3.766583113406648e-09</v>
+        <v>3.766583113406553e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.629655450108588e-09</v>
+        <v>4.629655450108476e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>2.924780658574284e-09</v>
+        <v>2.924780658574221e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>4.849547933315857e-09</v>
+        <v>4.849547933315993e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.387035116498097e-08</v>
+        <v>1.387035116498083e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.468381771521741e-09</v>
+        <v>8.468381771521602e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.119146786845526e-09</v>
+        <v>4.119146786845438e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.43958180199609e-09</v>
+        <v>4.439581801996093e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.307369077964024e-09</v>
+        <v>6.307369077964019e-09</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.321103833912999e-09</v>
+        <v>2.321103833912996e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.777041162652099e-09</v>
+        <v>2.777041162652095e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.78863055471104e-09</v>
+        <v>2.788630554711082e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.427140564228876e-09</v>
+        <v>2.427140564228875e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.331849290631331e-09</v>
+        <v>2.331849290631326e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.769837748975777e-09</v>
+        <v>2.769837748975757e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.78863055471104e-09</v>
+        <v>2.788630554711082e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78863055471104e-09</v>
+        <v>2.788630554711082e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.625095042643392e-09</v>
+        <v>2.625095042643407e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.78863055471104e-09</v>
+        <v>2.788630554711082e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.78863055471104e-09</v>
+        <v>2.788630554711082e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.722746182333113e-09</v>
+        <v>2.722746182333109e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.426219130555923e-09</v>
+        <v>2.426219130555751e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.410075419718295e-09</v>
+        <v>2.410075419718192e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.385662571318013e-09</v>
+        <v>2.385662571317955e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.229224162486123e-09</v>
+        <v>2.229224162486075e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.78863055471104e-09</v>
+        <v>2.788630554711082e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.78863055471104e-09</v>
+        <v>2.788630554711082e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.78863055471104e-09</v>
+        <v>2.788630554711082e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.444520789728638e-09</v>
+        <v>2.444520789728587e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.430374547161734e-09</v>
+        <v>2.43037454716173e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.672984920122978e-09</v>
+        <v>2.672984920123021e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.156336398474591e-09</v>
+        <v>2.156336398474433e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.253176035440964e-09</v>
+        <v>3.25317603544093e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.312419285030161e-09</v>
+        <v>2.312419285029992e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.78863055471104e-09</v>
+        <v>2.788630554711082e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.231945697023243e-09</v>
+        <v>3.231945697023238e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936036e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>3.346448364770538e-09</v>
+        <v>3.346448364770537e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.912142267936041e-09</v>
+        <v>3.912142267936033e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.519949094090998e-09</v>
+        <v>4.519949094091017e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>4.962015860270802e-09</v>
+        <v>4.962015860270795e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>6.778021073308223e-09</v>
+        <v>6.778021073308182e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>4.85047471084754e-09</v>
+        <v>4.850474710847544e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>9.911706305012257e-09</v>
+        <v>9.911706305012169e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>3.916418866472882e-08</v>
+        <v>3.916418866472863e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.940745710191166e-09</v>
+        <v>4.940745710191157e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>9.232224626627831e-09</v>
+        <v>9.232224626627817e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.883739984464018e-08</v>
+        <v>1.883739984464012e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.104432494831109e-08</v>
+        <v>1.104432494831107e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.908791706796845e-08</v>
+        <v>4.908791706796844e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>1.279717981794436e-08</v>
+        <v>1.279717981794432e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>4.35687649135605e-09</v>
+        <v>4.356876491356045e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>6.467837970900326e-09</v>
+        <v>6.467837970900318e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>7.357320117473318e-09</v>
+        <v>7.357320117473393e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.450027933192978e-09</v>
+        <v>7.450027933192983e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>6.245195214937228e-09</v>
+        <v>6.245195214937223e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>8.099803641986273e-09</v>
+        <v>8.09980364198626e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>8.148325584577713e-09</v>
+        <v>8.148325584577716e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.103437158148463e-08</v>
+        <v>1.103437158148458e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>6.345226509926627e-09</v>
+        <v>6.345226509926595e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>1.168273021676325e-08</v>
+        <v>1.168273021676324e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.828080026941863e-08</v>
+        <v>3.828080026941859e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.201169970663381e-08</v>
+        <v>2.201169970663366e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.187868632277888e-09</v>
+        <v>9.187868632277905e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.013267950570219e-08</v>
+        <v>1.013267950570218e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.577274589604715e-08</v>
+        <v>1.577274589604712e-08</v>
       </c>
     </row>
     <row r="10">
@@ -7194,85 +7194,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.886292797887926e-09</v>
+        <v>3.886292797887917e-09</v>
       </c>
       <c r="C10" t="n">
-        <v>5.264807343868004e-09</v>
+        <v>5.264807343867996e-09</v>
       </c>
       <c r="D10" t="n">
-        <v>5.264807343868004e-09</v>
+        <v>5.264807343867996e-09</v>
       </c>
       <c r="E10" t="n">
-        <v>4.53078901175591e-09</v>
+        <v>4.530789011755906e-09</v>
       </c>
       <c r="F10" t="n">
-        <v>4.101049253059463e-09</v>
+        <v>4.10104925305946e-09</v>
       </c>
       <c r="G10" t="n">
-        <v>5.550651315172181e-09</v>
+        <v>5.550651315172172e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>5.264807343868004e-09</v>
+        <v>5.264807343867996e-09</v>
       </c>
       <c r="I10" t="n">
-        <v>5.264807343868004e-09</v>
+        <v>5.264807343867996e-09</v>
       </c>
       <c r="J10" t="n">
-        <v>5.264807343868004e-09</v>
+        <v>5.264807343867996e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>5.264807343868004e-09</v>
+        <v>5.264807343867996e-09</v>
       </c>
       <c r="L10" t="n">
-        <v>5.264807343868004e-09</v>
+        <v>5.264807343867996e-09</v>
       </c>
       <c r="M10" t="n">
-        <v>5.264807343867902e-09</v>
+        <v>5.264807343867898e-09</v>
       </c>
       <c r="N10" t="n">
-        <v>4.196227950214498e-09</v>
+        <v>4.196227950214493e-09</v>
       </c>
       <c r="O10" t="n">
-        <v>4.489882845873599e-09</v>
+        <v>4.489882845873589e-09</v>
       </c>
       <c r="P10" t="n">
-        <v>4.417900935254359e-09</v>
+        <v>4.417900935254351e-09</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.615383226504243e-09</v>
+        <v>3.615383226504238e-09</v>
       </c>
       <c r="R10" t="n">
-        <v>5.264807343868004e-09</v>
+        <v>5.264807343867996e-09</v>
       </c>
       <c r="S10" t="n">
-        <v>5.264807343868004e-09</v>
+        <v>5.264807343867996e-09</v>
       </c>
       <c r="T10" t="n">
-        <v>5.264807343868004e-09</v>
+        <v>5.264807343867996e-09</v>
       </c>
       <c r="U10" t="n">
-        <v>4.591445904173026e-09</v>
+        <v>4.591445904173018e-09</v>
       </c>
       <c r="V10" t="n">
-        <v>4.887457390248725e-09</v>
+        <v>4.887457390248714e-09</v>
       </c>
       <c r="W10" t="n">
-        <v>5.26507826136894e-09</v>
+        <v>5.265078261368933e-09</v>
       </c>
       <c r="X10" t="n">
-        <v>3.741726823753341e-09</v>
+        <v>3.741726823753332e-09</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.634531626925969e-09</v>
+        <v>6.634531626925956e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.860686182420423e-09</v>
+        <v>3.860686182420421e-09</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.264807343868004e-09</v>
+        <v>5.264807343867996e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.704781056652473e-09</v>
+        <v>6.704781056652469e-09</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="C11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="D11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="E11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="F11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="G11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="I11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="J11" t="n">
-        <v>2.92139697084905e-08</v>
+        <v>2.921396970849058e-08</v>
       </c>
       <c r="K11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="L11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089635e-08</v>
       </c>
       <c r="M11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="O11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="P11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="R11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="S11" t="n">
-        <v>3.05265229198238e-08</v>
+        <v>3.052652291982403e-08</v>
       </c>
       <c r="T11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="U11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="V11" t="n">
-        <v>2.019246136935198e-08</v>
+        <v>2.019246136935211e-08</v>
       </c>
       <c r="W11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="X11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.080457586089609e-08</v>
+        <v>3.080457586089633e-08</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.11033283747035e-08</v>
+        <v>3.110332837470354e-08</v>
       </c>
       <c r="C12" t="n">
-        <v>3.132061543365668e-08</v>
+        <v>3.132061543365691e-08</v>
       </c>
       <c r="D12" t="n">
-        <v>3.221322818352383e-08</v>
+        <v>3.221322818352419e-08</v>
       </c>
       <c r="E12" t="n">
-        <v>3.126579012181548e-08</v>
+        <v>3.126579012181577e-08</v>
       </c>
       <c r="F12" t="n">
-        <v>3.375351417599131e-08</v>
+        <v>3.375351417599161e-08</v>
       </c>
       <c r="G12" t="n">
-        <v>4.813185325348448e-08</v>
+        <v>4.813185325348464e-08</v>
       </c>
       <c r="H12" t="n">
-        <v>3.131016061391475e-08</v>
+        <v>3.131016061391504e-08</v>
       </c>
       <c r="I12" t="n">
         <v>3.341953164935934e-08</v>
       </c>
       <c r="J12" t="n">
-        <v>3.655011341136819e-08</v>
+        <v>3.655011341136828e-08</v>
       </c>
       <c r="K12" t="n">
-        <v>3.431022504581024e-08</v>
+        <v>3.431022504581058e-08</v>
       </c>
       <c r="L12" t="n">
-        <v>5.300961816041167e-08</v>
+        <v>5.300961816041192e-08</v>
       </c>
       <c r="M12" t="n">
-        <v>3.517179779574989e-08</v>
+        <v>3.517179779575012e-08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.102317404292608e-08</v>
+        <v>3.102317404292637e-08</v>
       </c>
       <c r="O12" t="n">
-        <v>3.206076529959878e-08</v>
+        <v>3.206076529959899e-08</v>
       </c>
       <c r="P12" t="n">
-        <v>3.249796839742596e-08</v>
+        <v>3.249796839742626e-08</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.254353664675125e-08</v>
+        <v>3.254353664675149e-08</v>
       </c>
       <c r="R12" t="n">
-        <v>3.195133072242274e-08</v>
+        <v>3.195133072242265e-08</v>
       </c>
       <c r="S12" t="n">
-        <v>3.286291793379767e-08</v>
+        <v>3.286291793379792e-08</v>
       </c>
       <c r="T12" t="n">
-        <v>3.288676770267196e-08</v>
+        <v>3.288676770267221e-08</v>
       </c>
       <c r="U12" t="n">
-        <v>3.430533271286453e-08</v>
+        <v>3.430533271286479e-08</v>
       </c>
       <c r="V12" t="n">
-        <v>2.138838415652834e-08</v>
+        <v>2.138838415652807e-08</v>
       </c>
       <c r="W12" t="n">
-        <v>3.462401747223708e-08</v>
+        <v>3.462401747223698e-08</v>
       </c>
       <c r="X12" t="n">
-        <v>4.769764538938941e-08</v>
+        <v>4.769764538938963e-08</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.970096868000733e-08</v>
+        <v>3.970096868000748e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.339772955000107e-08</v>
+        <v>3.33977295500014e-08</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.386212812428768e-08</v>
+        <v>3.386212812428809e-08</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.66343642026736e-08</v>
+        <v>3.663436420267385e-08</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.079187018892081e-08</v>
+        <v>3.079187018892087e-08</v>
       </c>
       <c r="C13" t="n">
-        <v>3.146944514894039e-08</v>
+        <v>3.146944514894053e-08</v>
       </c>
       <c r="D13" t="n">
-        <v>3.146944514894039e-08</v>
+        <v>3.146944514894053e-08</v>
       </c>
       <c r="E13" t="n">
-        <v>3.110865646993455e-08</v>
+        <v>3.110865646993473e-08</v>
       </c>
       <c r="F13" t="n">
-        <v>3.08974284486803e-08</v>
+        <v>3.089742844868039e-08</v>
       </c>
       <c r="G13" t="n">
-        <v>3.160994473089479e-08</v>
+        <v>3.160994473089501e-08</v>
       </c>
       <c r="H13" t="n">
-        <v>3.146944514894039e-08</v>
+        <v>3.146944514894053e-08</v>
       </c>
       <c r="I13" t="n">
-        <v>3.146944514894039e-08</v>
+        <v>3.146944514894053e-08</v>
       </c>
       <c r="J13" t="n">
-        <v>2.987883899653478e-08</v>
+        <v>2.987883899653487e-08</v>
       </c>
       <c r="K13" t="n">
-        <v>3.146944514894039e-08</v>
+        <v>3.146944514894053e-08</v>
       </c>
       <c r="L13" t="n">
-        <v>3.146944514894039e-08</v>
+        <v>3.146944514894053e-08</v>
       </c>
       <c r="M13" t="n">
-        <v>3.146944514894034e-08</v>
+        <v>3.146944514894048e-08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.094421119907461e-08</v>
+        <v>3.094421119907455e-08</v>
       </c>
       <c r="O13" t="n">
-        <v>3.108855004900987e-08</v>
+        <v>3.108855004900993e-08</v>
       </c>
       <c r="P13" t="n">
-        <v>3.105316910917705e-08</v>
+        <v>3.10531691091773e-08</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.065871124436382e-08</v>
+        <v>3.065871124436402e-08</v>
       </c>
       <c r="R13" t="n">
-        <v>3.146944514894039e-08</v>
+        <v>3.146944514894053e-08</v>
       </c>
       <c r="S13" t="n">
-        <v>3.146944514894039e-08</v>
+        <v>3.146944514894053e-08</v>
       </c>
       <c r="T13" t="n">
-        <v>3.146944514894039e-08</v>
+        <v>3.146944514894053e-08</v>
       </c>
       <c r="U13" t="n">
-        <v>3.113847087528436e-08</v>
+        <v>3.113847087528451e-08</v>
       </c>
       <c r="V13" t="n">
-        <v>2.067185355780213e-08</v>
+        <v>2.06718535578021e-08</v>
       </c>
       <c r="W13" t="n">
-        <v>3.146957831178252e-08</v>
+        <v>3.146957831178262e-08</v>
       </c>
       <c r="X13" t="n">
-        <v>3.072081233579179e-08</v>
+        <v>3.072081233579186e-08</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.214269947116519e-08</v>
+        <v>3.214269947116542e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.077928388614857e-08</v>
+        <v>3.077928388614867e-08</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.146944514894039e-08</v>
+        <v>3.146944514894053e-08</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.217722885257587e-08</v>
+        <v>3.217722885257625e-08</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="C14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="D14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="E14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="F14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>2.795831419547435e-09</v>
+        <v>2.795831419547428e-09</v>
       </c>
       <c r="H14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="I14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="J14" t="n">
-        <v>2.799552480756683e-09</v>
+        <v>2.799552480756678e-09</v>
       </c>
       <c r="K14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="L14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923412e-09</v>
       </c>
       <c r="M14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="N14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="O14" t="n">
-        <v>2.795831419547435e-09</v>
+        <v>2.795831419547428e-09</v>
       </c>
       <c r="P14" t="n">
-        <v>2.795831419547435e-09</v>
+        <v>2.795831419547428e-09</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="R14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="S14" t="n">
-        <v>2.617297997851138e-09</v>
+        <v>2.617297997851134e-09</v>
       </c>
       <c r="T14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="U14" t="n">
-        <v>2.795831419547433e-09</v>
+        <v>2.795831419547428e-09</v>
       </c>
       <c r="V14" t="n">
-        <v>2.801309402440181e-09</v>
+        <v>2.801309402440176e-09</v>
       </c>
       <c r="W14" t="n">
-        <v>2.795831419547435e-09</v>
+        <v>2.795831419547428e-09</v>
       </c>
       <c r="X14" t="n">
-        <v>2.795831419547435e-09</v>
+        <v>2.795831419547428e-09</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.895350938923417e-09</v>
+        <v>2.895350938923411e-09</v>
       </c>
     </row>
     <row r="15">
@@ -7634,85 +7634,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.194103452730782e-09</v>
+        <v>3.19410345273079e-09</v>
       </c>
       <c r="C15" t="n">
-        <v>3.411390511684014e-09</v>
+        <v>3.411390511684012e-09</v>
       </c>
       <c r="D15" t="n">
-        <v>4.304003261551175e-09</v>
+        <v>4.304003261551157e-09</v>
       </c>
       <c r="E15" t="n">
-        <v>3.356565199842806e-09</v>
+        <v>3.356565199842802e-09</v>
       </c>
       <c r="F15" t="n">
-        <v>5.844289254018643e-09</v>
+        <v>5.844289254018622e-09</v>
       </c>
       <c r="G15" t="n">
-        <v>2.012310881213583e-08</v>
+        <v>2.012310881213576e-08</v>
       </c>
       <c r="H15" t="n">
-        <v>3.400935691942105e-09</v>
+        <v>3.400935691942101e-09</v>
       </c>
       <c r="I15" t="n">
-        <v>5.510306727386667e-09</v>
+        <v>5.510306727386671e-09</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01356961836344e-08</v>
+        <v>1.013569618363438e-08</v>
       </c>
       <c r="K15" t="n">
-        <v>6.401000123837577e-09</v>
+        <v>6.401000123837576e-09</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5100393238439e-08</v>
+        <v>2.510039323843898e-08</v>
       </c>
       <c r="M15" t="n">
-        <v>7.262572873777245e-09</v>
+        <v>7.262572873777213e-09</v>
       </c>
       <c r="N15" t="n">
-        <v>3.113949120953411e-09</v>
+        <v>3.113949120953402e-09</v>
       </c>
       <c r="O15" t="n">
-        <v>4.052020858250127e-09</v>
+        <v>4.052020858250107e-09</v>
       </c>
       <c r="P15" t="n">
-        <v>4.4892239560773e-09</v>
+        <v>4.48922395607726e-09</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.63431172477858e-09</v>
+        <v>4.634311724778578e-09</v>
       </c>
       <c r="R15" t="n">
         <v>4.042105800450072e-09</v>
       </c>
       <c r="S15" t="n">
-        <v>4.953693011824975e-09</v>
+        <v>4.953693011824978e-09</v>
       </c>
       <c r="T15" t="n">
-        <v>4.977542780699259e-09</v>
+        <v>4.977542780699257e-09</v>
       </c>
       <c r="U15" t="n">
-        <v>6.296588271515845e-09</v>
+        <v>6.296588271515827e-09</v>
       </c>
       <c r="V15" t="n">
-        <v>3.9972321896161e-09</v>
+        <v>3.997232189616078e-09</v>
       </c>
       <c r="W15" t="n">
-        <v>6.615273030888428e-09</v>
+        <v>6.615273030888413e-09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.968890094804072e-08</v>
+        <v>1.968890094804071e-08</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.179174375803464e-08</v>
+        <v>1.179174375803457e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.488504628028393e-09</v>
+        <v>5.488504628028396e-09</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.952903202315018e-09</v>
+        <v>5.952903202315021e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.725139280700897e-09</v>
+        <v>8.725139280700892e-09</v>
       </c>
     </row>
     <row r="16">
@@ -7722,85 +7722,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.882645266948132e-09</v>
+        <v>2.882645266948131e-09</v>
       </c>
       <c r="C16" t="n">
-        <v>3.560220226967707e-09</v>
+        <v>3.5602202269677e-09</v>
       </c>
       <c r="D16" t="n">
-        <v>3.560220226967707e-09</v>
+        <v>3.5602202269677e-09</v>
       </c>
       <c r="E16" t="n">
-        <v>3.199431547961869e-09</v>
+        <v>3.199431547961863e-09</v>
       </c>
       <c r="F16" t="n">
-        <v>2.988203526707624e-09</v>
+        <v>2.988203526707619e-09</v>
       </c>
       <c r="G16" t="n">
-        <v>3.601200289546119e-09</v>
+        <v>3.601200289546115e-09</v>
       </c>
       <c r="H16" t="n">
-        <v>3.560220226967707e-09</v>
+        <v>3.5602202269677e-09</v>
       </c>
       <c r="I16" t="n">
-        <v>3.560220226967707e-09</v>
+        <v>3.5602202269677e-09</v>
       </c>
       <c r="J16" t="n">
-        <v>3.46442176880097e-09</v>
+        <v>3.464421768800963e-09</v>
       </c>
       <c r="K16" t="n">
-        <v>3.560220226967707e-09</v>
+        <v>3.5602202269677e-09</v>
       </c>
       <c r="L16" t="n">
-        <v>3.560220226967707e-09</v>
+        <v>3.5602202269677e-09</v>
       </c>
       <c r="M16" t="n">
-        <v>3.560220226967656e-09</v>
+        <v>3.560220226967651e-09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.034986277101954e-09</v>
+        <v>3.03498627710195e-09</v>
       </c>
       <c r="O16" t="n">
-        <v>3.079805607661211e-09</v>
+        <v>3.079805607661206e-09</v>
       </c>
       <c r="P16" t="n">
-        <v>3.044424667828409e-09</v>
+        <v>3.044424667828405e-09</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.749486322391107e-09</v>
+        <v>2.749486322391103e-09</v>
       </c>
       <c r="R16" t="n">
-        <v>3.560220226967707e-09</v>
+        <v>3.5602202269677e-09</v>
       </c>
       <c r="S16" t="n">
-        <v>3.560220226967707e-09</v>
+        <v>3.5602202269677e-09</v>
       </c>
       <c r="T16" t="n">
-        <v>3.560220226967707e-09</v>
+        <v>3.5602202269677e-09</v>
       </c>
       <c r="U16" t="n">
-        <v>3.12972643393568e-09</v>
+        <v>3.129726433935674e-09</v>
       </c>
       <c r="V16" t="n">
-        <v>3.280701590890146e-09</v>
+        <v>3.280701590890138e-09</v>
       </c>
       <c r="W16" t="n">
-        <v>3.460833870433853e-09</v>
+        <v>3.460833870433846e-09</v>
       </c>
       <c r="X16" t="n">
-        <v>2.712067894443158e-09</v>
+        <v>2.712067894443156e-09</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.233474549192498e-09</v>
+        <v>4.23347454919249e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.870058964175907e-09</v>
+        <v>2.8700589641759e-09</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.560220226967707e-09</v>
+        <v>3.5602202269677e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.268003930603191e-09</v>
+        <v>4.26800393060318e-09</v>
       </c>
     </row>
   </sheetData>
@@ -9487,7 +9487,7 @@
         <v>5.437747914325155e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.258382462868193e-09</v>
+        <v>4.258382462868192e-09</v>
       </c>
       <c r="R2" t="n">
         <v>1.067545732266456e-08</v>
@@ -9745,10 +9745,10 @@
         <v>3.333302225255328e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.342645287430313e-08</v>
+        <v>3.342645287430312e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.340355077131297e-08</v>
+        <v>3.340355077131298e-08</v>
       </c>
       <c r="Q5" t="n">
         <v>3.314821796535186e-08</v>
@@ -9766,7 +9766,7 @@
         <v>3.345892092952625e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.163861547653655e-08</v>
+        <v>2.163861547653654e-08</v>
       </c>
       <c r="W5" t="n">
         <v>3.367309269102624e-08</v>
@@ -9775,7 +9775,7 @@
         <v>3.318841603805763e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.410906833016227e-08</v>
+        <v>3.410906833016228e-08</v>
       </c>
       <c r="Z5" t="n">
         <v>3.322626470670256e-08</v>
@@ -9784,7 +9784,7 @@
         <v>3.367300649463355e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.406901744735171e-08</v>
+        <v>3.40690174473517e-08</v>
       </c>
     </row>
     <row r="6">
@@ -10088,7 +10088,7 @@
         <v>5.734255041813746e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>7.359061289849613e-09</v>
+        <v>7.359061289849612e-09</v>
       </c>
       <c r="M9" t="n">
         <v>4.510542064755065e-09</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.040402809754709e-08</v>
+        <v>3.040402809754708e-08</v>
       </c>
       <c r="C12" t="n">
         <v>3.043402479600962e-08</v>
@@ -10352,7 +10352,7 @@
         <v>3.048519566023192e-08</v>
       </c>
       <c r="L12" t="n">
-        <v>3.128382925591143e-08</v>
+        <v>3.128382925591142e-08</v>
       </c>
       <c r="M12" t="n">
         <v>2.98837096085077e-08</v>
@@ -10361,7 +10361,7 @@
         <v>3.214534325226893e-08</v>
       </c>
       <c r="O12" t="n">
-        <v>3.298371725800967e-08</v>
+        <v>3.298371725800966e-08</v>
       </c>
       <c r="P12" t="n">
         <v>3.061396124327166e-08</v>
@@ -10455,7 +10455,7 @@
         <v>2.965206055620655e-08</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.928201301005724e-08</v>
+        <v>2.928201301005723e-08</v>
       </c>
       <c r="R13" t="n">
         <v>3.004257609860062e-08</v>
@@ -10649,7 +10649,7 @@
         <v>3.823972551307417e-09</v>
       </c>
       <c r="W15" t="n">
-        <v>6.463699766700907e-09</v>
+        <v>6.463699766700906e-09</v>
       </c>
       <c r="X15" t="n">
         <v>6.105846548426809e-09</v>
@@ -10713,7 +10713,7 @@
         <v>2.746443004146955e-09</v>
       </c>
       <c r="O16" t="n">
-        <v>2.783966377159201e-09</v>
+        <v>2.7839663771592e-09</v>
       </c>
       <c r="P16" t="n">
         <v>2.750774923435183e-09</v>
@@ -10731,7 +10731,7 @@
         <v>3.239173791472755e-09</v>
       </c>
       <c r="U16" t="n">
-        <v>2.83102152981886e-09</v>
+        <v>2.831021529818859e-09</v>
       </c>
       <c r="V16" t="n">
         <v>2.972938948782085e-09</v>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide particulate matter results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide particulate matter results.xlsx
@@ -586,82 +586,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.718412623911698e-09</v>
+        <v>7.718412623911779e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.248160175281887e-09</v>
+        <v>6.248160175281881e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.873455781642451e-08</v>
+        <v>1.873455781642445e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>4.572462661643887e-09</v>
+        <v>4.572462661643811e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.712233530367606e-08</v>
+        <v>1.712233530367604e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>6.297624685473966e-08</v>
+        <v>6.297624685473954e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.365541039706213e-08</v>
+        <v>1.365541039706194e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.405519998810889e-08</v>
+        <v>2.405519998810905e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.878296879574153e-08</v>
+        <v>2.878296879574151e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.957107238201107e-08</v>
+        <v>3.957107238201099e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>8.515662017631397e-08</v>
+        <v>8.515662017631409e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>2.372733917425794e-08</v>
+        <v>2.372733917425791e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.810023018372867e-08</v>
+        <v>2.81002301837285e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.234528960187126e-08</v>
+        <v>1.23452896018712e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>9.423315236836362e-09</v>
+        <v>9.423315236836279e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.153035136489785e-08</v>
+        <v>1.153035136489795e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26439369703845e-08</v>
+        <v>1.264393697038445e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>9.895364013649637e-09</v>
+        <v>9.895364013649584e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>2.026196472346501e-08</v>
+        <v>2.026196472346495e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.611555695330689e-08</v>
+        <v>1.611555695330681e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>7.301206604589532e-09</v>
+        <v>7.301206604589512e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.282171517336521e-08</v>
+        <v>1.282171517336515e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>2.121348106392416e-08</v>
+        <v>2.121348106392389e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.462647985564096e-09</v>
+        <v>9.462647985563932e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.207903139413507e-08</v>
+        <v>1.207903139413529e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.455533737966277e-08</v>
+        <v>2.455533737966266e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.825382769431819e-08</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.010300433940651e-09</v>
+        <v>4.010300433940812e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>5.399174670016433e-09</v>
+        <v>5.399174670016428e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>5.434087293129357e-09</v>
+        <v>5.434087293129164e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.521178197502438e-09</v>
+        <v>4.521178197502434e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>4.158826643663502e-09</v>
+        <v>4.1588266436635e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.729318773496515e-09</v>
+        <v>5.729318773496396e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>5.434087293129357e-09</v>
+        <v>5.434087293129164e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>5.434087293129357e-09</v>
+        <v>5.434087293129164e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>5.364057888654574e-09</v>
+        <v>5.364057888654475e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>5.434087293129357e-09</v>
+        <v>5.434087293129164e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>5.434087293129357e-09</v>
+        <v>5.434087293129164e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>5.366115263475956e-09</v>
+        <v>5.366115263475951e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>4.330414282847234e-09</v>
+        <v>4.330414282847249e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.633713209065418e-09</v>
+        <v>4.633713209065004e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>4.559367313523827e-09</v>
+        <v>4.559367313523621e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.730493819726097e-09</v>
+        <v>3.730493819726005e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>5.434087293129357e-09</v>
+        <v>5.434087293129164e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>5.434087293129357e-09</v>
+        <v>5.434087293129164e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>5.434087293129357e-09</v>
+        <v>5.434087293129164e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.738498929744622e-09</v>
+        <v>4.738498929744888e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.879634220240394e-09</v>
+        <v>4.879634220240393e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>5.434367107933074e-09</v>
+        <v>5.434367107932909e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.860986714434181e-09</v>
+        <v>3.860986714434259e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.84860222321542e-09</v>
+        <v>6.848602223215432e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.983852862015821e-09</v>
+        <v>3.983852862015782e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.434087293129357e-09</v>
+        <v>5.434087293129164e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.848889578236363e-09</v>
+        <v>6.848889578236356e-09</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.033237283603895e-08</v>
+        <v>4.033237283603876e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.977429570113632e-08</v>
+        <v>3.977429570113619e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.434762840060204e-08</v>
+        <v>4.434762840060189e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.908734359049713e-08</v>
+        <v>3.908734359049699e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.371341992863267e-08</v>
+        <v>4.371341992863255e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.047320454292612e-08</v>
+        <v>6.047320454292598e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.249633880860462e-08</v>
+        <v>4.249633880860443e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.628693999404622e-08</v>
+        <v>4.6286939994046e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.551118811578427e-08</v>
+        <v>4.551118811578423e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.194229328505118e-08</v>
+        <v>5.194229328505103e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.855769016354673e-08</v>
+        <v>6.85576901635466e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>4.612424155432111e-08</v>
+        <v>4.612424155432099e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>4.776130600120695e-08</v>
+        <v>4.776130600120713e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>4.201881516297266e-08</v>
+        <v>4.201881516297255e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>4.095378981847275e-08</v>
+        <v>4.09537898184726e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.17217797450838e-08</v>
+        <v>4.172177974508365e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>4.212766862190128e-08</v>
+        <v>4.212766862190116e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>4.112584605454462e-08</v>
+        <v>4.112584605454452e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>4.490435028250086e-08</v>
+        <v>4.490435028250072e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>4.339303333985651e-08</v>
+        <v>4.339303333985635e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.370015267471226e-08</v>
+        <v>2.370015267471223e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>4.21924666893107e-08</v>
+        <v>4.219246668931057e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>4.525116681532923e-08</v>
+        <v>4.525116681532889e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.096812614351557e-08</v>
+        <v>4.09681261435151e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.192176717281456e-08</v>
+        <v>4.192176717281443e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.646923420035783e-08</v>
+        <v>4.646923420035769e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.41263573724375e-08</v>
+        <v>4.412635737243739e-08</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.898080948564629e-08</v>
+        <v>3.898080948564611e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.94648504537582e-08</v>
+        <v>3.94648504537581e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.949976307687114e-08</v>
+        <v>3.949976307687116e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.906865100553014e-08</v>
+        <v>3.906865100553003e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.898837324726232e-08</v>
+        <v>3.898837324726219e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.960737148468188e-08</v>
+        <v>3.960737148468168e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.949976307687114e-08</v>
+        <v>3.949976307687116e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.949976307687114e-08</v>
+        <v>3.949976307687116e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.697527008888701e-08</v>
+        <v>3.697527008888709e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.949976307687114e-08</v>
+        <v>3.949976307687116e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.949976307687114e-08</v>
+        <v>3.949976307687116e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.943179104721788e-08</v>
+        <v>3.943179104721776e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.909748722460613e-08</v>
+        <v>3.909748722460582e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.920803612169682e-08</v>
+        <v>3.920803612169655e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.918093791578553e-08</v>
+        <v>3.918093791578522e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.88788232604202e-08</v>
+        <v>3.887882326042028e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.949976307687114e-08</v>
+        <v>3.949976307687116e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.949976307687114e-08</v>
+        <v>3.949976307687116e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.949976307687114e-08</v>
+        <v>3.949976307687116e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.924622928642834e-08</v>
+        <v>3.924622928642821e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.281751797615557e-08</v>
+        <v>2.281751797615556e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.949986506608133e-08</v>
+        <v>3.949986506608122e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.892638638821637e-08</v>
+        <v>3.892638638821602e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.001533715881459e-08</v>
+        <v>4.001533715881435e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.897116965624274e-08</v>
+        <v>3.897116965624266e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.949976307687114e-08</v>
+        <v>3.949976307687116e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.996939135267061e-08</v>
+        <v>3.996939135267052e-08</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.060594072254001e-09</v>
+        <v>4.060594072253978e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>3.502516937351354e-09</v>
+        <v>3.502516937351351e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>8.075849636817069e-09</v>
+        <v>8.075849636817022e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>2.815564826712143e-09</v>
+        <v>2.815564826712124e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>7.441641164847678e-09</v>
+        <v>7.441641164847676e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>2.407863232338764e-08</v>
+        <v>2.407863232338757e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.224560044819688e-09</v>
+        <v>6.224560044819588e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.001516123026123e-08</v>
+        <v>1.001516123026113e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.157573571637366e-08</v>
+        <v>1.157573571637358e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.567051452126623e-08</v>
+        <v>1.56705145212662e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.228591139976163e-08</v>
+        <v>3.228591139976172e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>9.852462790536122e-09</v>
+        <v>9.852462790536111e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.148952723742198e-08</v>
+        <v>1.148952723742225e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.624242943434159e-09</v>
+        <v>5.624242943434143e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>4.559217598934258e-09</v>
+        <v>4.559217598934224e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.450000981298818e-09</v>
+        <v>5.450000981298821e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>5.855889858116329e-09</v>
+        <v>5.855889858116288e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>4.854067290759643e-09</v>
+        <v>4.854067290759637e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>8.632571518715877e-09</v>
+        <v>8.632571518715838e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>6.998461120317964e-09</v>
+        <v>6.998461120317945e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>3.688059511172731e-09</v>
+        <v>3.688059511172723e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>5.797894469772202e-09</v>
+        <v>5.797894469772185e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>8.856594595790727e-09</v>
+        <v>8.856594595790562e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.696347379730609e-09</v>
+        <v>4.696347379730254e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.64998840902959e-09</v>
+        <v>5.649988409029575e-09</v>
       </c>
       <c r="AA6" t="n">
         <v>1.019745543657287e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.854578608652567e-09</v>
+        <v>7.854578608652565e-09</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.709030721861275e-09</v>
+        <v>2.709030721861216e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>3.193071689973232e-09</v>
+        <v>3.193071689973227e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>3.227984313086155e-09</v>
+        <v>3.227984313086253e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.796872241745173e-09</v>
+        <v>2.796872241745172e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.716594483477316e-09</v>
+        <v>2.71659448347731e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>3.212799265143372e-09</v>
+        <v>3.212799265143296e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>3.227984313086155e-09</v>
+        <v>3.227984313086253e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>3.227984313086155e-09</v>
+        <v>3.227984313086253e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>3.03981768947643e-09</v>
+        <v>3.039817689476508e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.227984313086155e-09</v>
+        <v>3.227984313086253e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>3.227984313086155e-09</v>
+        <v>3.227984313086253e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>3.160012283432859e-09</v>
+        <v>3.160012283432856e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.82570846082113e-09</v>
+        <v>2.825708460820927e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.813463902158311e-09</v>
+        <v>2.813463902158123e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.786365696246982e-09</v>
+        <v>2.786365696246783e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.607044496635219e-09</v>
+        <v>2.607044496635379e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>3.227984313086155e-09</v>
+        <v>3.227984313086253e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>3.227984313086155e-09</v>
+        <v>3.227984313086253e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>3.227984313086155e-09</v>
+        <v>3.227984313086253e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.851657066889826e-09</v>
+        <v>2.851657066889791e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.805424812616059e-09</v>
+        <v>2.805424812616053e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>3.105292846542818e-09</v>
+        <v>3.105292846542824e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.531814168677843e-09</v>
+        <v>2.531814168677582e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.743558395029608e-09</v>
+        <v>3.743558395029475e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.699390892457747e-09</v>
+        <v>2.699390892457761e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.227984313086155e-09</v>
+        <v>3.227984313086253e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.697612588885616e-09</v>
+        <v>3.697612588885613e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.308548901532809e-09</v>
+        <v>3.308548901532259e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>4.547359642831624e-09</v>
+        <v>4.547359642831629e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>3.852339463868146e-09</v>
+        <v>3.852339463867479e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>3.670559450170222e-09</v>
+        <v>3.670559450170218e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.212534126268576e-09</v>
+        <v>6.212534126268567e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.7442665508867e-09</v>
+        <v>6.744266550886305e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>4.208311019898525e-09</v>
+        <v>4.208311019897965e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>5.008401284343185e-09</v>
+        <v>5.008401284342615e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>6.265252385865031e-09</v>
+        <v>6.265252385864987e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.633153755241828e-09</v>
+        <v>5.633153755241265e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>8.169723726865113e-09</v>
+        <v>8.16972372686398e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>4.262058921530372e-09</v>
+        <v>4.262058921530363e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>4.180062068952012e-09</v>
+        <v>4.180062068952299e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>4.043309071996392e-09</v>
+        <v>4.043309071995557e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>5.514188422243404e-09</v>
+        <v>5.514188422243358e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.156637666463297e-09</v>
+        <v>4.156637666462721e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.005485479318442e-08</v>
+        <v>1.005485479318392e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>6.043630864420925e-09</v>
+        <v>6.043630864420402e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>4.676070161243654e-09</v>
+        <v>4.676070161243356e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>5.353403507282154e-09</v>
+        <v>5.353403507281554e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>9.292572167526741e-09</v>
+        <v>9.292572167526742e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.510143526475368e-08</v>
+        <v>1.510143526475334e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.476366926055105e-08</v>
+        <v>1.476366926055042e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.924527100414679e-09</v>
+        <v>8.92452710041414e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.003188336314817e-09</v>
+        <v>5.003188336314433e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.739615624009596e-09</v>
+        <v>8.739615624008867e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.270535948267498e-09</v>
+        <v>3.270535948267497e-09</v>
       </c>
     </row>
     <row r="3">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.150060379953901e-09</v>
+        <v>3.150060379953351e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>4.370894145824741e-09</v>
+        <v>4.37089414582474e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.357590991950832e-09</v>
+        <v>4.357590991950822e-09</v>
       </c>
       <c r="E3" t="n">
         <v>3.635367257766469e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.299809264880282e-09</v>
+        <v>3.299809264880278e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>4.607980330687777e-09</v>
+        <v>4.607980330687756e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.357590991950832e-09</v>
+        <v>4.357590991950822e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.357590991950832e-09</v>
+        <v>4.357590991950822e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.323812719835868e-09</v>
+        <v>4.323812719835475e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.357590991950832e-09</v>
+        <v>4.357590991950822e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.357590991950832e-09</v>
+        <v>4.357590991950822e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.300185776275563e-09</v>
+        <v>4.300185776275558e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.421552752134994e-09</v>
+        <v>3.421552752134639e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.678784187903079e-09</v>
+        <v>3.678784187902674e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.615730547415524e-09</v>
+        <v>3.615730547414859e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.912753054108659e-09</v>
+        <v>2.912753054108525e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.357590991950832e-09</v>
+        <v>4.357590991950822e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.357590991950832e-09</v>
+        <v>4.357590991950822e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.357590991950832e-09</v>
+        <v>4.357590991950822e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.768365871078384e-09</v>
+        <v>3.768365871078169e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>3.950858129515572e-09</v>
+        <v>3.950858129515567e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.357828306248587e-09</v>
+        <v>4.357828306248318e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.023425634080769e-09</v>
+        <v>3.023425634080098e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.558475420461054e-09</v>
+        <v>5.558475420460954e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.127629878843113e-09</v>
+        <v>3.127629878842655e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.357590991950832e-09</v>
+        <v>4.357590991950822e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.569272993535379e-09</v>
+        <v>5.569272993535376e-09</v>
       </c>
     </row>
     <row r="4">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.311561069701628e-08</v>
+        <v>3.311561069701568e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.357559697586925e-08</v>
+        <v>3.35755969758695e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.33138159714763e-08</v>
+        <v>3.331381597147555e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.319719542827456e-08</v>
+        <v>3.319719542827475e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.414969445290398e-08</v>
+        <v>3.414969445290413e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.436788943597222e-08</v>
+        <v>3.436788943597108e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.344356342362034e-08</v>
+        <v>3.34435634236198e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.373518692987627e-08</v>
+        <v>3.373518692987565e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.256533026573775e-08</v>
+        <v>3.256533026573783e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.396290186930488e-08</v>
+        <v>3.396290186930428e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>3.488745183805275e-08</v>
+        <v>3.488745183805212e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>3.342667221397735e-08</v>
+        <v>3.342667221397746e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.343326701271595e-08</v>
+        <v>3.343326701271596e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.338342215116072e-08</v>
+        <v>3.338342215116007e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.391954040238802e-08</v>
+        <v>3.391954040238801e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.34247290930724e-08</v>
+        <v>3.342472909307177e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.557455997539995e-08</v>
+        <v>3.557455997539914e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.411251595553496e-08</v>
+        <v>3.41125159555345e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.361405613793515e-08</v>
+        <v>3.361405613793502e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.386093618891686e-08</v>
+        <v>3.386093618891621e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.452972409712412e-08</v>
+        <v>2.452972409712413e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.741397929734712e-08</v>
+        <v>3.741397929734657e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.729086755506393e-08</v>
+        <v>3.729086755506332e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.516256880436313e-08</v>
+        <v>3.516256880436269e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.373328687153316e-08</v>
+        <v>3.373328687153285e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.509517074255351e-08</v>
+        <v>3.509517074255316e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.307018021498588e-08</v>
+        <v>3.307018021498596e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.305784349196649e-08</v>
+        <v>3.305784349196644e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.351127737437292e-08</v>
+        <v>3.351127737437299e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.349797422049898e-08</v>
+        <v>3.349797422049905e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.318436828739127e-08</v>
+        <v>3.318436828739122e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.308804044387e-08</v>
+        <v>3.308804044387026e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.358923819424879e-08</v>
+        <v>3.358923819424868e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.349797422049898e-08</v>
+        <v>3.349797422049905e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.349797422049898e-08</v>
+        <v>3.349797422049905e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.185769830500571e-08</v>
+        <v>3.185769830500572e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.349797422049898e-08</v>
+        <v>3.349797422049905e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.349797422049898e-08</v>
+        <v>3.349797422049905e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.344056900482393e-08</v>
+        <v>3.344056900482388e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.315679927360208e-08</v>
+        <v>3.315679927360211e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.325055711137575e-08</v>
+        <v>3.325055711137542e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.322757479983151e-08</v>
+        <v>3.322757479983092e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.297134775829924e-08</v>
+        <v>3.297134775829926e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.349797422049898e-08</v>
+        <v>3.349797422049905e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.349797422049898e-08</v>
+        <v>3.349797422049905e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.349797422049898e-08</v>
+        <v>3.349797422049905e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.328320858297179e-08</v>
+        <v>3.32832085829717e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.258273205584216e-08</v>
+        <v>2.258273205584217e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.349806071877411e-08</v>
+        <v>3.349806071877384e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.30116866141162e-08</v>
+        <v>3.301168661411581e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.393568249319439e-08</v>
+        <v>3.393568249319415e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.304966783770376e-08</v>
+        <v>3.304966783770374e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.349797422049898e-08</v>
+        <v>3.349797422049905e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.390804287485263e-08</v>
+        <v>3.390804287485289e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.113690041280869e-09</v>
+        <v>2.113690041279969e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>2.573676320134148e-09</v>
+        <v>2.573676320134149e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.311895315740938e-09</v>
+        <v>2.311895315740305e-09</v>
       </c>
       <c r="E6" t="n">
         <v>2.195274772539418e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>3.147773797168771e-09</v>
+        <v>3.147773797168767e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.252341371289194e-09</v>
+        <v>3.252341371288074e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>2.441642767884948e-09</v>
+        <v>2.441642767884051e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>2.73326627414078e-09</v>
+        <v>2.733266274139891e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>3.060539158737913e-09</v>
+        <v>3.060539158737795e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>2.960981213569473e-09</v>
+        <v>2.960981213568558e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.885531182317503e-09</v>
+        <v>3.885531182317553e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>2.424751558242074e-09</v>
+        <v>2.424751558242056e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.431346356980875e-09</v>
+        <v>2.431346356980282e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>2.26787408647766e-09</v>
+        <v>2.267874086477067e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>2.803992337704898e-09</v>
+        <v>2.803992337705002e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.422808437336957e-09</v>
+        <v>2.422808437336053e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>4.572639319664511e-09</v>
+        <v>4.572639319663483e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.110595299799716e-09</v>
+        <v>3.110595299798777e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>2.612135482199803e-09</v>
+        <v>2.612135482199287e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>2.745388124233743e-09</v>
+        <v>2.745388124233214e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>4.138600534706021e-09</v>
+        <v>4.138600534706024e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>6.298431232664085e-09</v>
+        <v>6.298431232663584e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>6.175319490380861e-09</v>
+        <v>6.175319490380293e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.160648148627804e-09</v>
+        <v>4.160648148627137e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.731366215797715e-09</v>
+        <v>2.731366215797158e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.093250086818044e-09</v>
+        <v>4.093250086818099e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.068259559250632e-09</v>
+        <v>2.068259559250629e-09</v>
       </c>
     </row>
     <row r="7">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.055922836231133e-09</v>
+        <v>2.055922836230532e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.509356718637624e-09</v>
+        <v>2.509356718637626e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.496053564763693e-09</v>
+        <v>2.496053564763341e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.182447631655838e-09</v>
+        <v>2.182447631655836e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.086119788134894e-09</v>
+        <v>2.086119788134891e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.473690129565817e-09</v>
+        <v>2.473690129565646e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.496053564763693e-09</v>
+        <v>2.496053564763341e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.496053564763693e-09</v>
+        <v>2.496053564763341e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.352907198006007e-09</v>
+        <v>2.352907198005543e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.496053564763693e-09</v>
+        <v>2.496053564763341e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.496053564763693e-09</v>
+        <v>2.496053564763341e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.438648349088565e-09</v>
+        <v>2.438648349088547e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.154878617866989e-09</v>
+        <v>2.154878617866313e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.135009046692741e-09</v>
+        <v>2.135009046692443e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.112026735148549e-09</v>
+        <v>2.112026735147886e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.969427102564055e-09</v>
+        <v>1.969427102563445e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.496053564763693e-09</v>
+        <v>2.496053564763341e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.496053564763693e-09</v>
+        <v>2.496053564763341e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.496053564763693e-09</v>
+        <v>2.496053564763341e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.167660518288761e-09</v>
+        <v>2.167660518288691e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.191608493424075e-09</v>
+        <v>2.191608493424072e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.38251265409109e-09</v>
+        <v>2.38251265409085e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.896138549433286e-09</v>
+        <v>1.896138549432801e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.933761837459079e-09</v>
+        <v>2.933761837458328e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.047747181968537e-09</v>
+        <v>2.047747181968038e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.496053564763693e-09</v>
+        <v>2.496053564763341e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.906122219117567e-09</v>
+        <v>2.906122219117562e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.08222008071086e-09</v>
+        <v>6.082220080711334e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>6.498033201019128e-09</v>
+        <v>6.498033201019308e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>8.653717121590284e-09</v>
+        <v>8.653717121590261e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>4.172964707823522e-09</v>
+        <v>4.172964707823861e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.073725319316419e-08</v>
+        <v>1.073725319316423e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>4.866404435453326e-08</v>
+        <v>4.866404435453306e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>6.963652157762663e-09</v>
+        <v>6.963652157762664e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>1.406843770519707e-08</v>
+        <v>1.406843770519703e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.408709683943261e-08</v>
+        <v>2.408709683943233e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.261015741667213e-08</v>
+        <v>3.261015741667212e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>6.918787738965747e-08</v>
+        <v>6.918787738965979e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.587047005288473e-08</v>
+        <v>1.587047005288474e-08</v>
       </c>
       <c r="N2" t="n">
         <v>1.440335359119795e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>8.380122494247022e-09</v>
+        <v>8.380122494247009e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.078098152977423e-08</v>
+        <v>1.078098152977427e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.705533540565235e-09</v>
+        <v>7.705533540565217e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>7.334609793135051e-09</v>
+        <v>7.334609793135037e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>8.67958790432943e-09</v>
+        <v>8.679587904329597e-09</v>
       </c>
       <c r="T2" t="n">
         <v>1.016595651509084e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.129215016714023e-08</v>
+        <v>1.129215016714019e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>5.367902228990669e-09</v>
+        <v>5.367902228990608e-09</v>
       </c>
       <c r="W2" t="n">
         <v>1.788087030257547e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>2.318311526293567e-08</v>
+        <v>2.318311526293543e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.936289777134863e-09</v>
+        <v>8.936289777134874e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.796088684288568e-09</v>
+        <v>9.796088684288633e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.313359392191985e-08</v>
+        <v>1.313359392192002e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.722762561821257e-08</v>
+        <v>1.722762561821287e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.708257528521486e-09</v>
+        <v>3.708257528521197e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>5.037419069426124e-09</v>
+        <v>5.037419069425977e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>5.055212490661291e-09</v>
+        <v>5.055212490661245e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.207323323597062e-09</v>
+        <v>4.20732332359707e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.845944275028286e-09</v>
+        <v>3.845944275028298e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.334512376663609e-09</v>
+        <v>5.334512376663505e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>5.055212490661291e-09</v>
+        <v>5.055212490661245e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>5.055212490661291e-09</v>
+        <v>5.055212490661245e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.994674611270925e-09</v>
+        <v>4.994674611270923e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>5.055212490661291e-09</v>
+        <v>5.055212490661245e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>5.055212490661291e-09</v>
+        <v>5.055212490661245e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.986225335924121e-09</v>
+        <v>4.986225335924136e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>4.011097054290445e-09</v>
+        <v>4.011097054290393e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.298029042070767e-09</v>
+        <v>4.298029042070354e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>4.22769507862065e-09</v>
+        <v>4.22769507862056e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.44355013567836e-09</v>
+        <v>3.44355013567807e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>5.055212490661291e-09</v>
+        <v>5.055212490661245e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>5.055212490661291e-09</v>
+        <v>5.055212490661245e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>5.055212490661291e-09</v>
+        <v>5.055212490661245e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.397195570069758e-09</v>
+        <v>4.397195570069492e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.54481543145456e-09</v>
+        <v>4.544815431454661e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>5.055477205801743e-09</v>
+        <v>5.0554772058017e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.567001234358225e-09</v>
+        <v>3.567001234358156e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.393456365544026e-09</v>
+        <v>6.393456365543731e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.683237148529785e-09</v>
+        <v>3.683237148529544e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.055212490661291e-09</v>
+        <v>5.055212490661245e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.409893036445816e-09</v>
+        <v>6.409893036445813e-09</v>
       </c>
     </row>
     <row r="4">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.711528154609273e-08</v>
+        <v>3.711528154609262e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.725553261758506e-08</v>
+        <v>3.725553261758492e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.805256202145044e-08</v>
+        <v>3.805256202145035e-08</v>
       </c>
       <c r="E4" t="n">
         <v>3.633633464230135e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.87661323146996e-08</v>
+        <v>3.876613231469949e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.263585647287532e-08</v>
+        <v>5.263585647287522e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.743655318788002e-08</v>
+        <v>3.743655318787997e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.002616409131589e-08</v>
+        <v>4.002616409131573e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.136501608514689e-08</v>
+        <v>4.136501608514666e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.678440319828304e-08</v>
+        <v>4.678440319828299e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.011655261116288e-08</v>
+        <v>6.011655261116298e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>4.063914157459242e-08</v>
+        <v>4.063914157459241e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>4.014823699898233e-08</v>
+        <v>4.014823699898235e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.795283999249415e-08</v>
+        <v>3.795283999249404e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.882792491863365e-08</v>
+        <v>3.882792491863358e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.770696024030054e-08</v>
+        <v>3.770696024030052e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.757176288996885e-08</v>
+        <v>3.757176288996873e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.806199161796881e-08</v>
+        <v>3.806199161796871e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.860375552276991e-08</v>
+        <v>3.860375552276979e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.901423988450837e-08</v>
+        <v>3.901423988450827e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.159098224390134e-08</v>
+        <v>2.15909822439015e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>4.141575100521654e-08</v>
+        <v>4.141575100521647e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>4.334835703116396e-08</v>
+        <v>4.334835703116408e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.815555643626081e-08</v>
+        <v>3.81555564362607e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.846894304164984e-08</v>
+        <v>3.846894304164967e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.968542450980128e-08</v>
+        <v>3.968542450980124e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.11443968562143e-08</v>
+        <v>4.114439685621427e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.625000007229538e-08</v>
+        <v>3.625000007229526e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.67231559180165e-08</v>
+        <v>3.672315591801607e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.674094933925162e-08</v>
+        <v>3.674094933925123e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.634885795429155e-08</v>
+        <v>3.634885795429147e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.625433113587398e-08</v>
+        <v>3.625433113587386e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.684275086799461e-08</v>
+        <v>3.684275086799437e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.674094933925162e-08</v>
+        <v>3.674094933925123e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.674094933925162e-08</v>
+        <v>3.674094933925123e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.440605237752298e-08</v>
+        <v>3.440605237752283e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.674094933925162e-08</v>
+        <v>3.674094933925123e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.674094933925162e-08</v>
+        <v>3.674094933925123e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.667196218451461e-08</v>
+        <v>3.667196218451443e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.636038152331691e-08</v>
+        <v>3.636038152331674e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.646496486353728e-08</v>
+        <v>3.646496486353707e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.643932895976291e-08</v>
+        <v>3.643932895976258e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.615351733595518e-08</v>
+        <v>3.615351733595513e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.674094933925162e-08</v>
+        <v>3.674094933925123e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.674094933925162e-08</v>
+        <v>3.674094933925123e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.674094933925162e-08</v>
+        <v>3.674094933925123e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.65011098985208e-08</v>
+        <v>3.650110989852052e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.129097677137259e-08</v>
+        <v>2.129097677137251e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.67410458248119e-08</v>
+        <v>3.674104582481177e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.619851381178804e-08</v>
+        <v>3.619851381178798e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.722872351719339e-08</v>
+        <v>3.722872351719303e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.624088043759259e-08</v>
+        <v>3.624088043759238e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.674094933925162e-08</v>
+        <v>3.674094933925123e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.720146035838973e-08</v>
+        <v>3.720146035838968e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.345716448609309e-09</v>
+        <v>3.34571644860926e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>3.485967520101666e-09</v>
+        <v>3.485967520101693e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>4.282996923967072e-09</v>
+        <v>4.282996923966887e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>2.566769544817966e-09</v>
+        <v>2.56676954481808e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.996567217216253e-09</v>
+        <v>4.996567217216274e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.874689756877434e-08</v>
+        <v>1.874689756877424e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.666988090396677e-09</v>
+        <v>3.666988090396487e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>6.256598993832501e-09</v>
+        <v>6.256598993832306e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>9.754874238400636e-09</v>
+        <v>9.754874238400498e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.301483810079965e-08</v>
+        <v>1.301483810079948e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.634698751367953e-08</v>
+        <v>2.634698751367947e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.869576477109047e-09</v>
+        <v>6.869576477109049e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>6.378671901498932e-09</v>
+        <v>6.378671901498757e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>4.063881088393118e-09</v>
+        <v>4.063881088393087e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>4.938966014532618e-09</v>
+        <v>4.938966014532607e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.937395142817188e-09</v>
+        <v>3.937395142816975e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>3.802197792485433e-09</v>
+        <v>3.802197792485244e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>4.29242652048542e-09</v>
+        <v>4.292426520485261e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.834190425286527e-09</v>
+        <v>4.834190425286353e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>5.125280980407335e-09</v>
+        <v>5.125280980407327e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>2.882525424310475e-09</v>
+        <v>2.882525424310376e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>7.526792101115481e-09</v>
+        <v>7.526792101115483e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>9.459398127062959e-09</v>
+        <v>9.459398127063067e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.385991338777427e-09</v>
+        <v>4.385991338777249e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.699377944166442e-09</v>
+        <v>4.699377944166448e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.91585941231788e-09</v>
+        <v>5.91585941231775e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.374831758730968e-09</v>
+        <v>7.374831758731026e-09</v>
       </c>
     </row>
     <row r="7">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.480434974812009e-09</v>
+        <v>2.480434974811696e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.953590820533086e-09</v>
+        <v>2.953590820532543e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.971384241768263e-09</v>
+        <v>2.97138424176819e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.579292856808184e-09</v>
+        <v>2.57929285680819e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.484766038390604e-09</v>
+        <v>2.484766038390609e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.953791963893586e-09</v>
+        <v>2.953791963893462e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.971384241768263e-09</v>
+        <v>2.97138424176819e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.971384241768263e-09</v>
+        <v>2.97138424176819e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.795910530776625e-09</v>
+        <v>2.795910530776521e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.971384241768263e-09</v>
+        <v>2.97138424176819e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.971384241768263e-09</v>
+        <v>2.97138424176819e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.902397087031182e-09</v>
+        <v>2.902397087031194e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.590816425833533e-09</v>
+        <v>2.590816425833305e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.57600595943631e-09</v>
+        <v>2.576005959436063e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.55037005566185e-09</v>
+        <v>2.550370055661623e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.383952238471822e-09</v>
+        <v>2.383952238471491e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.971384241768263e-09</v>
+        <v>2.97138424176819e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.971384241768263e-09</v>
+        <v>2.97138424176819e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.971384241768263e-09</v>
+        <v>2.97138424176819e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.612150994419753e-09</v>
+        <v>2.612150994419628e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.582519951781711e-09</v>
+        <v>2.58251995178183e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.852086920710818e-09</v>
+        <v>2.852086920710821e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.309554907687016e-09</v>
+        <v>2.309554907687053e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.459158419710029e-09</v>
+        <v>3.459158419709826e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.471315340109191e-09</v>
+        <v>2.471315340108998e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.971384241768263e-09</v>
+        <v>2.97138424176819e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.431895260906337e-09</v>
+        <v>3.431895260906345e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.458853221863303e-09</v>
+        <v>4.458853221863273e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.316474615628572e-09</v>
+        <v>5.316474615628574e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.030864505352272e-08</v>
+        <v>1.030864505352268e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>5.32610341725782e-09</v>
+        <v>5.326103417257816e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>9.00154625766883e-09</v>
+        <v>9.001546257668841e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>4.193936102380576e-08</v>
+        <v>4.193936102380583e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>4.425626905016746e-09</v>
+        <v>4.4256269050167e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>1.032996693433062e-08</v>
+        <v>1.032996693433057e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.071186796346419e-08</v>
+        <v>2.071186796346424e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>9.770296104459348e-09</v>
+        <v>9.7702961044593e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>5.720908491437804e-08</v>
+        <v>5.720908491437792e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.376877902219156e-08</v>
+        <v>1.376877902219157e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>7.346435634956407e-09</v>
+        <v>7.346435634956342e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>5.758675434486378e-09</v>
+        <v>5.758675434486353e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>8.679318692443512e-09</v>
+        <v>8.679318692443484e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.342235463032403e-09</v>
+        <v>7.342235463032429e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>4.192211064419984e-09</v>
+        <v>4.192211064419951e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>7.334929551110525e-09</v>
+        <v>7.334929551110466e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>6.755941481280743e-09</v>
+        <v>6.75594148128071e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>9.279525412314147e-09</v>
+        <v>9.279525412314139e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>5.165030558069251e-09</v>
+        <v>5.165030558069352e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.568582545374802e-08</v>
+        <v>1.568582545374794e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.288874823190017e-08</v>
+        <v>3.28887482319001e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.496593303772757e-08</v>
+        <v>1.496593303772752e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.441411253745343e-09</v>
+        <v>9.441411253745291e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.209925434411683e-09</v>
+        <v>9.209925434411627e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.636567450922124e-08</v>
+        <v>1.636567450922117e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.569490571286297e-09</v>
+        <v>3.569490571286397e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>4.858130990869391e-09</v>
+        <v>4.858130990869392e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.874077219907202e-09</v>
+        <v>4.874077219907218e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.060105001133954e-09</v>
+        <v>4.060105001133958e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.70237564697277e-09</v>
+        <v>3.702375646972771e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.144591760097579e-09</v>
+        <v>5.144591760097675e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.874077219907202e-09</v>
+        <v>4.874077219907218e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.874077219907202e-09</v>
+        <v>4.874077219907218e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.817602115734042e-09</v>
+        <v>4.81760211573417e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.874077219907202e-09</v>
+        <v>4.874077219907218e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.874077219907202e-09</v>
+        <v>4.874077219907218e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.806345061354212e-09</v>
+        <v>4.806345061354213e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.86280431457843e-09</v>
+        <v>3.862804314578507e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.140710889662164e-09</v>
+        <v>4.140710889662374e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>4.072589272948741e-09</v>
+        <v>4.072589272948814e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.313109519060088e-09</v>
+        <v>3.313109519060238e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.874077219907202e-09</v>
+        <v>4.874077219907218e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.874077219907202e-09</v>
+        <v>4.874077219907218e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.874077219907202e-09</v>
+        <v>4.874077219907218e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.236764720162348e-09</v>
+        <v>4.236764720162662e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.385393555121912e-09</v>
+        <v>4.385393555122016e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.8743336084613e-09</v>
+        <v>4.874333608461388e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.432677477619353e-09</v>
+        <v>3.432677477619527e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.170238034134011e-09</v>
+        <v>6.170238034133867e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.545257204470942e-09</v>
+        <v>3.545257204470899e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.874077219907202e-09</v>
+        <v>4.874077219907218e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.1895106140613e-09</v>
+        <v>6.18951061406128e-09</v>
       </c>
     </row>
     <row r="4">
@@ -2814,85 +2814,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.553638257514439e-08</v>
+        <v>3.553638257514438e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.583884148666938e-08</v>
+        <v>3.583884148666939e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.766856300606044e-08</v>
+        <v>3.766856300606042e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.577665689968101e-08</v>
+        <v>3.577665689968106e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.714742987446605e-08</v>
+        <v>3.714742987446609e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.919758755060925e-08</v>
+        <v>4.919758755060923e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.552427197281693e-08</v>
+        <v>3.552427197281689e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.767633458124074e-08</v>
+        <v>3.767633458124073e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.941828118715844e-08</v>
+        <v>3.941828118715854e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.747234113573936e-08</v>
+        <v>3.747234113573935e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.476322260257206e-08</v>
+        <v>5.4763222602572e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>3.888669662458432e-08</v>
+        <v>3.888669662458436e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.658887245701224e-08</v>
+        <v>3.65888724570122e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.60101525083625e-08</v>
+        <v>3.601015250836241e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.707469267996323e-08</v>
+        <v>3.707469267996319e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.658734154366678e-08</v>
+        <v>3.658734154366682e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.543919463982655e-08</v>
+        <v>3.543919463982654e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.658467862456159e-08</v>
+        <v>3.658467862456152e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.637364427192979e-08</v>
+        <v>3.63736442719298e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.729346098137283e-08</v>
+        <v>3.729346098137281e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.232505679447693e-08</v>
+        <v>2.232505679447728e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.962848211990247e-08</v>
+        <v>3.96284821199024e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>4.589874546562071e-08</v>
+        <v>4.589874546562067e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.936608978766655e-08</v>
+        <v>3.936608978766649e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.735246646961505e-08</v>
+        <v>3.735246646961502e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.726809260671166e-08</v>
+        <v>3.726809260671164e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.984620895905659e-08</v>
+        <v>3.984620895905655e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.521222033243257e-08</v>
+        <v>3.521222033243259e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.567178061758723e-08</v>
+        <v>3.567178061758724e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.568772684662504e-08</v>
+        <v>3.568772684662518e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.531521534310784e-08</v>
+        <v>3.531521534310782e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.521594441287033e-08</v>
+        <v>3.521594441287039e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.578632621998224e-08</v>
+        <v>3.578632621998243e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.568772684662504e-08</v>
+        <v>3.568772684662518e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.568772684662504e-08</v>
+        <v>3.568772684662518e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.362500792555347e-08</v>
+        <v>3.362500792555354e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.568772684662504e-08</v>
+        <v>3.568772684662518e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.568772684662504e-08</v>
+        <v>3.568772684662518e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.561999468807216e-08</v>
+        <v>3.56199946880722e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.531912974759872e-08</v>
+        <v>3.531912974759883e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.542042343087308e-08</v>
+        <v>3.542042343087315e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.539559390150531e-08</v>
+        <v>3.539559390150527e-08</v>
       </c>
       <c r="Q5" t="n">
         <v>3.511877244947443e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.568772684662504e-08</v>
+        <v>3.568772684662518e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.568772684662504e-08</v>
+        <v>3.568772684662518e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.568772684662504e-08</v>
+        <v>3.568772684662518e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.54554339241692e-08</v>
+        <v>3.545543392416932e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.204088826186253e-08</v>
+        <v>2.204088826186245e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.568782029724235e-08</v>
+        <v>3.568782029724251e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.516235356633152e-08</v>
+        <v>3.516235356633163e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.616016224312197e-08</v>
+        <v>3.616016224312193e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.520338755479099e-08</v>
+        <v>3.5203387554791e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.568772684662504e-08</v>
+        <v>3.568772684662518e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.613711671382025e-08</v>
+        <v>3.613711671382022e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.705306016132661e-09</v>
+        <v>2.705306016132611e-09</v>
       </c>
       <c r="C6" t="n">
         <v>3.007764927657655e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>4.837486447048731e-09</v>
+        <v>4.837486447048683e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>2.945580340669325e-09</v>
+        <v>2.945580340669324e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.316353315454368e-09</v>
+        <v>4.316353315454375e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.625001796490411e-08</v>
+        <v>1.625001796490406e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.693195413805205e-09</v>
+        <v>2.69319541380515e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.845258022229055e-09</v>
+        <v>4.845258022228989e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>8.481315136936084e-09</v>
+        <v>8.481315136936219e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.641264576727658e-09</v>
+        <v>4.641264576727606e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>2.193214604356042e-08</v>
+        <v>2.193214604356036e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.055620065572651e-09</v>
+        <v>6.05562006557266e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.757795898000474e-09</v>
+        <v>3.757795898000417e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.062582922657401e-09</v>
+        <v>3.062582922657306e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>4.12712309425813e-09</v>
+        <v>4.127123094258011e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.756264984655082e-09</v>
+        <v>3.756264984655059e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>2.608118080814902e-09</v>
+        <v>2.608118080814814e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.753602065549905e-09</v>
+        <v>3.753602065549852e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>3.54256771291815e-09</v>
+        <v>3.542567712918084e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.345891395667768e-09</v>
+        <v>4.345891395667728e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>2.769057921670043e-09</v>
+        <v>2.769057921670149e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>6.680912534197323e-09</v>
+        <v>6.68091253419724e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.295117587991561e-08</v>
+        <v>1.295117587991552e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.535013228654774e-09</v>
+        <v>6.53501322865473e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.521389910603343e-09</v>
+        <v>4.521389910603243e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.437016047699911e-09</v>
+        <v>4.437016047699858e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.015132400044785e-09</v>
+        <v>7.015132400044778e-09</v>
       </c>
     </row>
     <row r="7">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.381143773420904e-09</v>
+        <v>2.381143773420854e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.840704058575511e-09</v>
+        <v>2.840704058575512e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.856650287613292e-09</v>
+        <v>2.856650287613439e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.484138784096136e-09</v>
+        <v>2.484138784096139e-09</v>
       </c>
       <c r="F7" t="n">
         <v>2.384867853858628e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.838756634277159e-09</v>
+        <v>2.838756634277344e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.856650287613292e-09</v>
+        <v>2.856650287613439e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.856650287613292e-09</v>
+        <v>2.856650287613439e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.688041875331163e-09</v>
+        <v>2.688041875331164e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.856650287613292e-09</v>
+        <v>2.856650287613439e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.856650287613292e-09</v>
+        <v>2.856650287613439e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.788918129060456e-09</v>
+        <v>2.788918129060459e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.488053188586965e-09</v>
+        <v>2.488053188587127e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.472853845167941e-09</v>
+        <v>2.472853845168009e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.448024315800219e-09</v>
+        <v>2.448024315800174e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.287695890462765e-09</v>
+        <v>2.287695890462712e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.856650287613292e-09</v>
+        <v>2.856650287613439e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.856650287613292e-09</v>
+        <v>2.856650287613439e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.856650287613292e-09</v>
+        <v>2.856650287613439e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.50786433846414e-09</v>
+        <v>2.50786433846419e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.484889389055634e-09</v>
+        <v>2.484889389055669e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.740250711537256e-09</v>
+        <v>2.740250711537396e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.214783980626395e-09</v>
+        <v>2.214783980626489e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.329085684110238e-09</v>
+        <v>3.32908568411017e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.372310995779216e-09</v>
+        <v>2.372310995779249e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.856650287613292e-09</v>
+        <v>2.856650287613439e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.306040154808487e-09</v>
+        <v>3.306040154808488e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.077919370254451e-09</v>
+        <v>4.077919370254212e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>4.477668525083474e-09</v>
+        <v>4.477668525083472e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>6.179031957221545e-09</v>
+        <v>6.17903195722131e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>4.272924230147875e-09</v>
+        <v>4.272924230147876e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>9.032803863534488e-09</v>
+        <v>9.032803863534491e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>3.631402543672493e-08</v>
+        <v>3.631402543672477e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>4.469466262815282e-09</v>
+        <v>4.469466262815037e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>8.462642942309324e-09</v>
+        <v>8.462642942309075e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.734803353821483e-08</v>
+        <v>1.734803353821475e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.014878352143104e-08</v>
+        <v>1.014878352143082e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>4.554795192339038e-08</v>
+        <v>4.554795192339025e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.171391244872188e-08</v>
+        <v>1.171391244872194e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.926182002557818e-09</v>
+        <v>3.926182002557578e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>5.890409793387948e-09</v>
+        <v>5.890409793387693e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>6.718063717287516e-09</v>
+        <v>6.718063717287418e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.804327379523211e-09</v>
+        <v>6.804327379522965e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>5.683243015155627e-09</v>
+        <v>5.683243015155386e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>7.40893694601018e-09</v>
+        <v>7.408936946010007e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>7.454086110988732e-09</v>
+        <v>7.454086110988505e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.013952201669858e-08</v>
+        <v>1.013952201669833e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>5.655411115377088e-09</v>
+        <v>5.655411115377071e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.074281301095865e-08</v>
+        <v>1.07428130109584e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.549204168525488e-08</v>
+        <v>3.549204168525472e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.035381213114148e-08</v>
+        <v>2.035381213114141e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.42137014901745e-09</v>
+        <v>8.421370149017364e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.300506880143139e-09</v>
+        <v>9.300506880142894e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.450347462358138e-08</v>
+        <v>1.450347462358139e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3410,82 +3410,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.488308750213363e-09</v>
+        <v>3.488308750213283e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>4.759412864178051e-09</v>
+        <v>4.759412864178052e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.77100225623721e-09</v>
+        <v>4.771002256236992e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.975459998530397e-09</v>
+        <v>3.975459998530394e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.626047664983361e-09</v>
+        <v>3.62604766498336e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.036977110689878e-09</v>
+        <v>5.036977110689629e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.77100225623721e-09</v>
+        <v>4.771002256236992e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.77100225623721e-09</v>
+        <v>4.771002256236992e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.718876804675242e-09</v>
+        <v>4.718876804675231e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.77100225623721e-09</v>
+        <v>4.771002256236992e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.77100225623721e-09</v>
+        <v>4.771002256236992e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.705117883859012e-09</v>
+        <v>4.705117883859064e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.776700199064647e-09</v>
+        <v>3.776700199064571e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.049943037722151e-09</v>
+        <v>4.049943037721878e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.982964615498242e-09</v>
+        <v>3.982964615497962e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.236230200192369e-09</v>
+        <v>3.236230200192287e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.77100225623721e-09</v>
+        <v>4.771002256236992e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.77100225623721e-09</v>
+        <v>4.771002256236992e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.77100225623721e-09</v>
+        <v>4.771002256236992e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.144446411453241e-09</v>
+        <v>4.144446411453037e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.298972049466955e-09</v>
+        <v>4.298972049466927e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.771254342165552e-09</v>
+        <v>4.771254342165376e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.353791608732915e-09</v>
+        <v>3.353791608732861e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.045516513663648e-09</v>
+        <v>6.045516513663496e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.464482059760964e-09</v>
+        <v>3.464482059760736e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.77100225623721e-09</v>
+        <v>4.771002256236992e-09</v>
       </c>
       <c r="AB3" t="n">
         <v>6.065827268853429e-09</v>
@@ -3498,85 +3498,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.499340540176769e-08</v>
+        <v>3.499340540176753e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.513174407986826e-08</v>
+        <v>3.513174407986822e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.575923626720755e-08</v>
+        <v>3.575923626720738e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.499295820405922e-08</v>
+        <v>3.499295820405919e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.675994385607359e-08</v>
+        <v>3.675994385607355e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.674308752752732e-08</v>
+        <v>4.67430875275272e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.513611964633037e-08</v>
+        <v>3.513611964633023e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6591585655758e-08</v>
+        <v>3.659158565575784e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.79472646315528e-08</v>
+        <v>3.794726463155274e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.72061640971856e-08</v>
+        <v>3.720616409718538e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.010874530167769e-08</v>
+        <v>5.01087453016776e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>3.773476492021176e-08</v>
+        <v>3.773476492021175e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.493809891303244e-08</v>
+        <v>3.493809891303228e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.565403687766276e-08</v>
+        <v>3.565403687766261e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.595570701412108e-08</v>
+        <v>3.595570701412098e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.598714910604699e-08</v>
+        <v>3.598714910604682e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.557852701967222e-08</v>
+        <v>3.557852701967206e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.620752219334756e-08</v>
+        <v>3.62075221933473e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.622397853381393e-08</v>
+        <v>3.622397853381375e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.720278838746462e-08</v>
+        <v>3.720278838746446e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.31500465978907e-08</v>
+        <v>2.315004659789074e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.742268087067192e-08</v>
+        <v>3.742268087067178e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>4.644348410233705e-08</v>
+        <v>4.644348410233694e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.092577719192897e-08</v>
+        <v>4.092577719192884e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.657654220725287e-08</v>
+        <v>3.657654220725265e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.68969772224033e-08</v>
+        <v>3.689697722240316e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.876476449837117e-08</v>
+        <v>3.876476449837115e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3586,82 +3586,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.477849925432029e-08</v>
+        <v>3.47784992543201e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.52344365830592e-08</v>
+        <v>3.523443658305916e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.524602597511827e-08</v>
+        <v>3.524602597511813e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.488453598463602e-08</v>
+        <v>3.488453598463598e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.478924471103842e-08</v>
+        <v>3.47892447110384e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.534297068633192e-08</v>
+        <v>3.534297068633168e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.524602597511827e-08</v>
+        <v>3.524602597511813e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.524602597511827e-08</v>
+        <v>3.524602597511813e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.334408530122331e-08</v>
+        <v>3.334408530122325e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.524602597511827e-08</v>
+        <v>3.524602597511813e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.524602597511827e-08</v>
+        <v>3.524602597511813e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.518014160274023e-08</v>
+        <v>3.518014160274026e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.488361455096321e-08</v>
+        <v>3.4883614550963e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.498320835707437e-08</v>
+        <v>3.498320835707417e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.495879550867406e-08</v>
+        <v>3.495879550867392e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.468661958289348e-08</v>
+        <v>3.468661958289323e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.524602597511827e-08</v>
+        <v>3.524602597511813e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.524602597511827e-08</v>
+        <v>3.524602597511813e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.524602597511827e-08</v>
+        <v>3.524602597511813e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.501765372708481e-08</v>
+        <v>3.501765372708455e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.26556404864781e-08</v>
+        <v>2.26556404864783e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.524611785747912e-08</v>
+        <v>3.524611785747888e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.472946933583061e-08</v>
+        <v>3.472946933583048e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.571057145584818e-08</v>
+        <v>3.571057145584809e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.47698147054375e-08</v>
+        <v>3.476981470543728e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.524602597511827e-08</v>
+        <v>3.524602597511813e-08</v>
       </c>
       <c r="AB5" t="n">
         <v>3.568934111743032e-08</v>
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.536009981360646e-09</v>
+        <v>2.536009981360454e-09</v>
       </c>
       <c r="C6" t="n">
         <v>2.674348659461183e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>3.301840846800489e-09</v>
+        <v>3.301840846800313e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>2.535562783652087e-09</v>
+        <v>2.53556278365209e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.302548435666489e-09</v>
+        <v>4.302548435666485e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.416995459017162e-08</v>
+        <v>1.41699545901713e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.678724225923326e-09</v>
+        <v>2.678724225923137e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.134190235350939e-09</v>
+        <v>4.134190235350757e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.228274372972989e-09</v>
+        <v>7.228274372972917e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.748768676778473e-09</v>
+        <v>4.748768676778317e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.765134988127062e-08</v>
+        <v>1.765134988127045e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.277369499804623e-09</v>
+        <v>5.277369499804604e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.48070349262535e-09</v>
+        <v>2.48070349262517e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.080903940306945e-09</v>
+        <v>3.080903940306705e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>3.382574076765268e-09</v>
+        <v>3.38257407676508e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.529753685639882e-09</v>
+        <v>3.529753685639703e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>3.121131599265162e-09</v>
+        <v>3.121131599264973e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.750126772940536e-09</v>
+        <v>3.750126772940255e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>3.766583113406851e-09</v>
+        <v>3.766583113406652e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.629655450108837e-09</v>
+        <v>4.629655450108582e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>2.924780658574305e-09</v>
+        <v>2.924780658574291e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>4.849547933316106e-09</v>
+        <v>4.849547933315859e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.387035116498105e-08</v>
+        <v>1.387035116498097e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.468381771521878e-09</v>
+        <v>8.468381771521743e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.119146786845765e-09</v>
+        <v>4.119146786845536e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.439581801996273e-09</v>
+        <v>4.43958180199609e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.307369077964019e-09</v>
+        <v>6.30736907796402e-09</v>
       </c>
     </row>
     <row r="7">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.321103833913081e-09</v>
+        <v>2.321103833912997e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.777041162652097e-09</v>
+        <v>2.777041162652094e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.788630554711296e-09</v>
+        <v>2.788630554711041e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.42714056422888e-09</v>
+        <v>2.427140564228876e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.33184929063133e-09</v>
+        <v>2.331849290631328e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.76983774897591e-09</v>
+        <v>2.769837748975781e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.788630554711296e-09</v>
+        <v>2.788630554711041e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.788630554711296e-09</v>
+        <v>2.788630554711041e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.625095042643418e-09</v>
+        <v>2.625095042643393e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.788630554711296e-09</v>
+        <v>2.788630554711041e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.788630554711296e-09</v>
+        <v>2.788630554711041e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.722746182333114e-09</v>
+        <v>2.722746182333088e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.426219130556018e-09</v>
+        <v>2.426219130555926e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.410075419718483e-09</v>
+        <v>2.410075419718294e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.385662571318206e-09</v>
+        <v>2.385662571318014e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.229224162486269e-09</v>
+        <v>2.229224162486126e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.788630554711296e-09</v>
+        <v>2.788630554711041e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.788630554711296e-09</v>
+        <v>2.788630554711041e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.788630554711296e-09</v>
+        <v>2.788630554711041e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.444520789729001e-09</v>
+        <v>2.444520789728657e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.430374547161704e-09</v>
+        <v>2.430374547161731e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.672984920123118e-09</v>
+        <v>2.672984920122977e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.156336398474789e-09</v>
+        <v>2.156336398474596e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.253176035441188e-09</v>
+        <v>3.253176035440982e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.312419285030389e-09</v>
+        <v>2.312419285030171e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.788630554711296e-09</v>
+        <v>2.788630554711041e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.231945697023245e-09</v>
+        <v>3.231945697023242e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4006,85 +4006,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.376859084860338e-09</v>
+        <v>4.376859084860348e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>3.116774993637637e-09</v>
+        <v>3.116774993637632e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.208649620924257e-08</v>
+        <v>1.208649620924259e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>5.958179585770403e-09</v>
+        <v>5.958179585770408e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>5.485694115528702e-09</v>
+        <v>5.485694115528704e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.460685573497726e-08</v>
+        <v>1.460685573497728e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>6.938336040766497e-09</v>
+        <v>6.93833604076653e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>8.65567702203647e-09</v>
+        <v>8.655677022036491e-09</v>
       </c>
       <c r="J2" t="n">
         <v>1.005044069197401e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.782219735845249e-08</v>
+        <v>1.782219735845252e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.199864811702691e-08</v>
+        <v>2.19986481170269e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>7.9415578643749e-09</v>
+        <v>7.941557864374897e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.313349210153579e-08</v>
+        <v>1.313349210153582e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>4.873212871814848e-09</v>
+        <v>4.873212871814871e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>9.259032576438714e-09</v>
+        <v>9.25903257643875e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.133024959717286e-09</v>
+        <v>8.133024959717306e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>7.767510418844571e-09</v>
+        <v>7.767510418844592e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>7.135939809538069e-09</v>
+        <v>7.135939809538102e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>6.148411976203702e-09</v>
+        <v>6.148411976203724e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>6.057743014702575e-09</v>
+        <v>6.057743014702613e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>4.198220970506488e-09</v>
+        <v>4.198220970506475e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>7.840084094537479e-09</v>
+        <v>7.840084094537507e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>8.687082570858892e-09</v>
+        <v>8.687082570858922e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.629776663330302e-09</v>
+        <v>4.629776663330311e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.314251224791056e-09</v>
+        <v>7.314251224791081e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.219894466676721e-09</v>
+        <v>8.219894466676723e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.280236378528745e-08</v>
+        <v>5.280236378528751e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4094,85 +4094,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.279942554944976e-09</v>
+        <v>3.279942554945054e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>4.521291440670293e-09</v>
+        <v>4.521291440670291e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.522536683143224e-09</v>
+        <v>4.522536683143272e-09</v>
       </c>
       <c r="E3" t="n">
         <v>3.770307912572898e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.418345819750231e-09</v>
+        <v>3.418345819750229e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>4.780196670381226e-09</v>
+        <v>4.780196670381317e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.522536683143224e-09</v>
+        <v>4.522536683143272e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.522536683143224e-09</v>
+        <v>4.522536683143272e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.478491362347288e-09</v>
+        <v>4.478491362347296e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.522536683143224e-09</v>
+        <v>4.522536683143272e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.522536683143224e-09</v>
+        <v>4.522536683143272e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.462024533479698e-09</v>
+        <v>4.462024533479701e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55931835227105e-09</v>
+        <v>3.559318352271086e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.824019113057006e-09</v>
+        <v>3.824019113057049e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.759134560523423e-09</v>
+        <v>3.759134560523472e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.035744447883005e-09</v>
+        <v>3.035744447883015e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.522536683143224e-09</v>
+        <v>4.522536683143272e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.522536683143224e-09</v>
+        <v>4.522536683143272e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.522536683143224e-09</v>
+        <v>4.522536683143272e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.915874577758645e-09</v>
+        <v>3.91587457775866e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.079317333787974e-09</v>
+        <v>4.079317333787949e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.522780888417327e-09</v>
+        <v>4.522780888417368e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.149630668781195e-09</v>
+        <v>3.149630668781214e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.757731493818621e-09</v>
+        <v>5.757731493818618e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.256860731019784e-09</v>
+        <v>3.256860731019808e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.522536683143224e-09</v>
+        <v>4.522536683143272e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.929135378232323e-09</v>
+        <v>5.929135378232317e-09</v>
       </c>
     </row>
     <row r="4">
@@ -4182,13 +4182,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.465694265010831e-08</v>
+        <v>3.465694265010833e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.419686542929819e-08</v>
+        <v>3.41968654292982e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.746701485081582e-08</v>
+        <v>3.746701485081581e-08</v>
       </c>
       <c r="E4" t="n">
         <v>3.517574817545369e-08</v>
@@ -4197,64 +4197,64 @@
         <v>3.502603349114869e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.838565630239031e-08</v>
+        <v>3.838565630239029e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.559057092215505e-08</v>
+        <v>3.559057092215515e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.621652154379198e-08</v>
+        <v>3.621652154379212e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.464125140017789e-08</v>
+        <v>3.464125140017793e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.955761056769941e-08</v>
+        <v>3.955761056769945e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.107987782683892e-08</v>
+        <v>4.107987782683894e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>3.591777731475434e-08</v>
+        <v>3.591777731475433e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.78486325591101e-08</v>
+        <v>3.784863255911013e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.483785777697278e-08</v>
+        <v>3.48378577769728e-08</v>
       </c>
       <c r="P4" t="n">
         <v>3.643643755841306e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.602602100436704e-08</v>
+        <v>3.602602100436709e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.589279524630739e-08</v>
+        <v>3.589279524630743e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.566259517549172e-08</v>
+        <v>3.566259517549174e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.530265287637864e-08</v>
+        <v>3.530265287637865e-08</v>
       </c>
       <c r="U4" t="n">
         <v>3.526960510460017e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.081131103941364e-08</v>
+        <v>2.081131103941363e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.591924749889439e-08</v>
+        <v>3.591924749889433e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.622796849755523e-08</v>
+        <v>3.622796849755526e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.474912813755242e-08</v>
+        <v>3.474912813755246e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.57275875925131e-08</v>
+        <v>3.572758759251312e-08</v>
       </c>
       <c r="AA4" t="n">
         <v>3.605768391958052e-08</v>
@@ -4270,61 +4270,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.425712945559835e-08</v>
+        <v>3.425712945559843e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.470879518157679e-08</v>
+        <v>3.47087951815768e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.471004042404963e-08</v>
+        <v>3.471004042404962e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.437829464185946e-08</v>
+        <v>3.437829464185949e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.427250931336677e-08</v>
+        <v>3.427250931336678e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.480395446380156e-08</v>
+        <v>3.480395446380162e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.471004042404963e-08</v>
+        <v>3.471004042404962e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.471004042404963e-08</v>
+        <v>3.471004042404962e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.261034129866131e-08</v>
+        <v>3.261034129866133e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.471004042404963e-08</v>
+        <v>3.471004042404962e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.471004042404963e-08</v>
+        <v>3.471004042404962e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.464952827438625e-08</v>
+        <v>3.464952827438626e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.435895865312744e-08</v>
+        <v>3.435895865312747e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.445543897216068e-08</v>
+        <v>3.445543897216075e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.443178931467506e-08</v>
+        <v>3.44317893146751e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.416812211309317e-08</v>
+        <v>3.416812211309323e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.471004042404963e-08</v>
+        <v>3.471004042404962e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.471004042404963e-08</v>
+        <v>3.471004042404962e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.471004042404963e-08</v>
+        <v>3.471004042404962e-08</v>
       </c>
       <c r="U5" t="n">
         <v>3.448891921042308e-08</v>
@@ -4336,19 +4336,19 @@
         <v>3.471012943400446e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.420963230329108e-08</v>
+        <v>3.420963230329106e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.516025442815103e-08</v>
+        <v>3.516025442815107e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.424871640181808e-08</v>
+        <v>3.424871640181818e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.471004042404963e-08</v>
+        <v>3.471004042404962e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.529174902653883e-08</v>
+        <v>3.529174902653886e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4358,85 +4358,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.553687827920619e-09</v>
+        <v>2.553687827920611e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>2.093610607110483e-09</v>
+        <v>2.093610607110484e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>5.363760028628132e-09</v>
+        <v>5.363760028628112e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>3.072493353266027e-09</v>
+        <v>3.072493353266025e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.922778668961008e-09</v>
+        <v>2.92277866896101e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>6.165634128232097e-09</v>
+        <v>6.165634128232063e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>3.487316099967408e-09</v>
+        <v>3.487316099967488e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.113266721604367e-09</v>
+        <v>4.11326672160445e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>4.481239511791605e-09</v>
+        <v>4.481239511791655e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>7.454355745511763e-09</v>
+        <v>7.454355745511773e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>8.976623004651298e-09</v>
+        <v>8.976623004651278e-09</v>
       </c>
       <c r="M6" t="n">
         <v>3.81452249256664e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>5.745377736922501e-09</v>
+        <v>5.745377736922499e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>2.61783560281457e-09</v>
+        <v>2.617835602814575e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>4.21641538425487e-09</v>
+        <v>4.216415384254847e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.922766182179396e-09</v>
+        <v>3.922766182179407e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>3.789540424119727e-09</v>
+        <v>3.789540424119732e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.559340353304043e-09</v>
+        <v>3.559340353304049e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>3.199398054190945e-09</v>
+        <v>3.199398054190948e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>3.049582930441951e-09</v>
+        <v>3.049582930441952e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>2.312491910634783e-09</v>
+        <v>2.312491910634784e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>3.699225324736179e-09</v>
+        <v>3.699225324736136e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>4.007946323397038e-09</v>
+        <v>4.007946323397046e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.645873315364767e-09</v>
+        <v>2.645873315364771e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.624332770325401e-09</v>
+        <v>3.624332770325396e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.954429097392862e-09</v>
+        <v>3.95442909739286e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.027323554548566e-08</v>
+        <v>2.027323554548564e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.15387463341071e-09</v>
+        <v>2.153874633410767e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.605540359389085e-09</v>
+        <v>2.605540359389087e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.606785601862019e-09</v>
+        <v>2.606785601862011e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.275039819671819e-09</v>
+        <v>2.275039819671817e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.169254491179088e-09</v>
+        <v>2.169254491179089e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.583932289643401e-09</v>
+        <v>2.583932289643468e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.606785601862019e-09</v>
+        <v>2.606785601862011e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.606785601862019e-09</v>
+        <v>2.606785601862011e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.450329410275084e-09</v>
+        <v>2.450329410275077e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.606785601862019e-09</v>
+        <v>2.606785601862011e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.606785601862019e-09</v>
+        <v>2.606785601862011e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.546273452198583e-09</v>
+        <v>2.546273452198582e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.255703830939787e-09</v>
+        <v>2.255703830939778e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.235416798002463e-09</v>
+        <v>2.235416798002532e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.211767140516853e-09</v>
+        <v>2.211767140516893e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.064867290905524e-09</v>
+        <v>2.064867290905563e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.606785601862019e-09</v>
+        <v>2.606785601862011e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.606785601862019e-09</v>
+        <v>2.606785601862011e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.606785601862019e-09</v>
+        <v>2.606785601862011e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.268897036264883e-09</v>
+        <v>2.268897036264877e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.26915293128788e-09</v>
+        <v>2.26915293128787e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.49010725984628e-09</v>
+        <v>2.490107259846284e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.989610129132886e-09</v>
+        <v>1.989610129132837e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.056999605963417e-09</v>
+        <v>3.056999605963484e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.145461579630394e-09</v>
+        <v>2.145461579630452e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.606785601862019e-09</v>
+        <v>2.606785601862011e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.188494204351163e-09</v>
+        <v>3.188494204351168e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4690,85 +4690,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.040330803881311e-09</v>
+        <v>5.040330803881234e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.101727639425482e-09</v>
+        <v>5.10172763942549e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>5.654150419825689e-09</v>
+        <v>5.654150419825621e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>5.660101418384428e-09</v>
+        <v>5.660101418384421e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>7.916785228813928e-09</v>
+        <v>7.916785228813925e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>7.050960669417913e-09</v>
+        <v>7.050960669417702e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>5.585843721517705e-09</v>
+        <v>5.585843721517632e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.54811567339681e-09</v>
+        <v>6.548115673396764e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>6.740421640723579e-09</v>
+        <v>6.740421640723518e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.193986283642042e-09</v>
+        <v>5.193986283641972e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>6.705851667275414e-09</v>
+        <v>6.705851667275331e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>3.98707422243823e-09</v>
+        <v>3.98707422243822e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>8.336753742588854e-09</v>
+        <v>8.336753742588803e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>9.923850309368097e-09</v>
+        <v>9.923850309368019e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>5.437747914325168e-09</v>
+        <v>5.437747914325095e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.258382462868213e-09</v>
+        <v>4.258382462868119e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.067545732266459e-08</v>
+        <v>1.067545732266449e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>6.156244731154186e-09</v>
+        <v>6.156244731154107e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>4.136829042978343e-09</v>
+        <v>4.136829042978368e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>3.169586995627e-09</v>
+        <v>3.169586995626916e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>5.543818042076559e-09</v>
+        <v>5.543818042076427e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.064561571978747e-08</v>
+        <v>1.06456157197874e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>9.968176283157989e-09</v>
+        <v>9.968176283157933e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.104190238690383e-09</v>
+        <v>5.104190238690306e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.79008292422204e-09</v>
+        <v>8.790082924221942e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.125094849183093e-09</v>
+        <v>6.125094849183022e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.840253033995068e-09</v>
+        <v>2.840253033995062e-09</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.152762326067136e-09</v>
+        <v>3.15276232606722e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>4.360689773897399e-09</v>
+        <v>4.360689773897303e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.356078641176817e-09</v>
+        <v>4.356078641176602e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.629517043658358e-09</v>
+        <v>3.629517043658345e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.297417587934256e-09</v>
+        <v>3.297417587934247e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>4.605594117999903e-09</v>
+        <v>4.605594117999894e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.356078641176817e-09</v>
+        <v>4.356078641176602e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.356078641176817e-09</v>
+        <v>4.356078641176602e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.31469085517026e-09</v>
+        <v>4.314690855170174e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.356078641176817e-09</v>
+        <v>4.356078641176602e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.356078641176817e-09</v>
+        <v>4.356078641176602e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.287818829589899e-09</v>
+        <v>4.287818829589884e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.423307186484122e-09</v>
+        <v>3.423307186484153e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.679640881332048e-09</v>
+        <v>3.679640881331885e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.616807298836531e-09</v>
+        <v>3.616807298836503e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.916283205749433e-09</v>
+        <v>2.916283205749531e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.356078641176817e-09</v>
+        <v>4.356078641176602e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.356078641176817e-09</v>
+        <v>4.356078641176602e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.356078641176817e-09</v>
+        <v>4.356078641176602e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.768719348369511e-09</v>
+        <v>3.768719348369474e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>3.932756034508234e-09</v>
+        <v>3.932756034508114e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.356315127238468e-09</v>
+        <v>4.356315127238323e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.026569537033669e-09</v>
+        <v>3.026569537033528e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.55244594977139e-09</v>
+        <v>5.55244594977123e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.130410107685695e-09</v>
+        <v>3.130410107685655e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.356078641176817e-09</v>
+        <v>4.356078641176602e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.550905300548008e-09</v>
+        <v>5.550905300547984e-09</v>
       </c>
     </row>
     <row r="4">
@@ -4866,82 +4866,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.392240837304478e-08</v>
+        <v>3.392240837304471e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.394771722763315e-08</v>
+        <v>3.394771722763298e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.41461384152226e-08</v>
+        <v>3.414613841522256e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.409376077723347e-08</v>
+        <v>3.409376077723348e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.494363765615768e-08</v>
+        <v>3.494363765615767e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.465525934902484e-08</v>
+        <v>3.465525934902482e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.412124142578712e-08</v>
+        <v>3.412124142578705e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.447197825267928e-08</v>
+        <v>3.447197825267922e-08</v>
       </c>
       <c r="J4" t="n">
         <v>3.274410317221188e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.397841399110377e-08</v>
+        <v>3.397841399110374e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>3.452947117021845e-08</v>
+        <v>3.45294711702184e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>3.349512880526144e-08</v>
+        <v>3.349512880526143e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.512391582565122e-08</v>
+        <v>3.512391582565114e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.570239388761342e-08</v>
+        <v>3.570239388761337e-08</v>
       </c>
       <c r="P4" t="n">
         <v>3.406726224309416e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.363739738484644e-08</v>
+        <v>3.363739738484664e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.597634581814485e-08</v>
+        <v>3.597634581814477e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.432914589581277e-08</v>
+        <v>3.432914589581271e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.359309259064889e-08</v>
+        <v>3.359309259064887e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.324054422231894e-08</v>
+        <v>3.324054422231884e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.222582866025021e-08</v>
+        <v>2.222582866025014e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.596546890431387e-08</v>
+        <v>3.596546890431382e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.571855018455794e-08</v>
+        <v>3.571855018455788e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.394568438715728e-08</v>
+        <v>3.394568438715724e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.528914898909643e-08</v>
+        <v>3.528914898909637e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.431779212961471e-08</v>
+        <v>3.431779212961467e-08</v>
       </c>
       <c r="AB4" t="n">
         <v>3.308101652627916e-08</v>
@@ -4954,82 +4954,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.323441182782961e-08</v>
+        <v>3.323441182782917e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.367761762735408e-08</v>
+        <v>3.367761762735389e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.367300649463353e-08</v>
+        <v>3.367300649463338e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.335363661697139e-08</v>
+        <v>3.335363661697141e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.325993239441051e-08</v>
+        <v>3.325993239441052e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.376395195597682e-08</v>
+        <v>3.376395195597674e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.367300649463353e-08</v>
+        <v>3.367300649463338e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.367300649463353e-08</v>
+        <v>3.367300649463338e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.185995278524676e-08</v>
+        <v>3.185995278524672e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.367300649463353e-08</v>
+        <v>3.367300649463338e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.367300649463353e-08</v>
+        <v>3.367300649463338e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.360474668304667e-08</v>
+        <v>3.360474668304669e-08</v>
       </c>
       <c r="N5" t="n">
         <v>3.333302225255343e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.342645287430325e-08</v>
+        <v>3.342645287430333e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.340355077131283e-08</v>
+        <v>3.340355077131289e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.314821796535186e-08</v>
+        <v>3.314821796535182e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.367300649463353e-08</v>
+        <v>3.367300649463338e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.367300649463353e-08</v>
+        <v>3.367300649463338e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.367300649463353e-08</v>
+        <v>3.367300649463338e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.345892092952623e-08</v>
+        <v>3.345892092952629e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.163861547653671e-08</v>
+        <v>2.163861547653665e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.367309269102602e-08</v>
+        <v>3.367309269102595e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.318841603805748e-08</v>
+        <v>3.31884160380573e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.410906833016199e-08</v>
+        <v>3.410906833016183e-08</v>
       </c>
       <c r="Z5" t="n">
         <v>3.322626470670254e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.367300649463353e-08</v>
+        <v>3.367300649463338e-08</v>
       </c>
       <c r="AB5" t="n">
         <v>3.406901744735176e-08</v>
@@ -5042,85 +5042,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.751043717561753e-09</v>
+        <v>2.751043717561729e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>2.776352572150193e-09</v>
+        <v>2.776352572150112e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.97477375973964e-09</v>
+        <v>2.974773759739605e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>2.922396121750537e-09</v>
+        <v>2.922396121750532e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>3.772273000674707e-09</v>
+        <v>3.772273000674705e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.370060009333852e-09</v>
+        <v>3.370060009333742e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>2.949876770304129e-09</v>
+        <v>2.949876770304088e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>3.30061359719633e-09</v>
+        <v>3.30061359719629e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>3.234832157723468e-09</v>
+        <v>3.234832157723393e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>2.807049335620801e-09</v>
+        <v>2.807049335620766e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.358106514735504e-09</v>
+        <v>3.358106514735485e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>2.323764149778446e-09</v>
+        <v>2.32376414977844e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.952551170168175e-09</v>
+        <v>3.95255117016817e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>4.417194547922314e-09</v>
+        <v>4.417194547922277e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>2.782062903403104e-09</v>
+        <v>2.782062903403052e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.466032729363482e-09</v>
+        <v>2.46603272936371e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>4.804981162661833e-09</v>
+        <v>4.804981162661807e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.157781240329801e-09</v>
+        <v>3.157781240329761e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>2.421727935165945e-09</v>
+        <v>2.421727935165954e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.955344882627829e-09</v>
+        <v>1.955344882627797e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>2.767014611738892e-09</v>
+        <v>2.767014611738908e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>4.680269564622818e-09</v>
+        <v>4.68026956462277e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>4.433350844866883e-09</v>
+        <v>4.433350844866839e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.774319731674311e-09</v>
+        <v>2.774319731674292e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.117784333613475e-09</v>
+        <v>4.117784333613433e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.146427474131723e-09</v>
+        <v>3.146427474131694e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.909651870796209e-09</v>
+        <v>1.909651870796204e-09</v>
       </c>
     </row>
     <row r="7">
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.063047172346622e-09</v>
+        <v>2.063047172346238e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.506252971871153e-09</v>
+        <v>2.506252971871002e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5016418391505e-09</v>
+        <v>2.501641839150399e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.182271961488459e-09</v>
+        <v>2.182271961488451e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.088567738927538e-09</v>
+        <v>2.088567738927531e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.478752616285782e-09</v>
+        <v>2.478752616285656e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5016418391505e-09</v>
+        <v>2.501641839150399e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5016418391505e-09</v>
+        <v>2.501641839150399e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.350681770758275e-09</v>
+        <v>2.350681770758141e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5016418391505e-09</v>
+        <v>2.501641839150399e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.5016418391505e-09</v>
+        <v>2.501641839150399e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.433382027563754e-09</v>
+        <v>2.433382027563746e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.161657597070488e-09</v>
+        <v>2.161657597070466e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.141253534612209e-09</v>
+        <v>2.141253534612239e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.118351431621766e-09</v>
+        <v>2.118351431621771e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.9768533098688e-09</v>
+        <v>1.976853309868837e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5016418391505e-09</v>
+        <v>2.501641839150399e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5016418391505e-09</v>
+        <v>2.501641839150399e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5016418391505e-09</v>
+        <v>2.501641839150399e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.173721589835183e-09</v>
+        <v>2.173721589835228e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.179801428025498e-09</v>
+        <v>2.179801428025436e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.38789335133494e-09</v>
+        <v>2.387893351334845e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.903216698366313e-09</v>
+        <v>1.903216698366176e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.937703674679026e-09</v>
+        <v>2.937703674678863e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.054900051219646e-09</v>
+        <v>2.054900051219578e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.5016418391505e-09</v>
+        <v>2.501641839150399e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.897652791868807e-09</v>
+        <v>2.897652791868799e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5374,85 +5374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.976683492859611e-09</v>
+        <v>6.976683492859512e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.454362001057561e-09</v>
+        <v>5.454362001057563e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>5.912068454311008e-09</v>
+        <v>5.912068454310875e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>8.100576035917744e-09</v>
+        <v>8.100576035917749e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.704127096676758e-09</v>
+        <v>6.704127096676757e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>5.210807112629886e-09</v>
+        <v>5.21080711262975e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>4.449157064569768e-09</v>
+        <v>4.449157064569788e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>4.750200046691743e-09</v>
+        <v>4.750200046691645e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>6.197896698037849e-09</v>
+        <v>6.197896698037921e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>4.180544949254428e-09</v>
+        <v>4.180544949254327e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>6.797180360840435e-09</v>
+        <v>6.797180360840351e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>3.727045009371184e-09</v>
+        <v>3.727045009371202e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>5.186556500012215e-09</v>
+        <v>5.186556500012116e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.037923115933246e-08</v>
+        <v>1.037923115933235e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>6.579457825538849e-09</v>
+        <v>6.579457825538815e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.833741060682792e-09</v>
+        <v>3.83374106068269e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18680126385381e-08</v>
+        <v>1.186801263853801e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>5.910731183846716e-09</v>
+        <v>5.910731183846496e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>3.734423928471206e-09</v>
+        <v>3.734423928471099e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>3.897903309440487e-09</v>
+        <v>3.897903309440365e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.009764395906634e-08</v>
+        <v>1.009764395906635e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.248181701589593e-08</v>
+        <v>1.248181701589583e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.134761563001926e-08</v>
+        <v>1.134761563001921e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.339357554752649e-09</v>
+        <v>5.339357554752578e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.017178169993343e-09</v>
+        <v>7.0171781699932e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.126346904670841e-09</v>
+        <v>6.126346904670791e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.678074668351827e-09</v>
+        <v>3.678074668351761e-09</v>
       </c>
     </row>
     <row r="3">
@@ -5462,85 +5462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.14282044199483e-09</v>
+        <v>3.142820441994804e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>4.354147944757674e-09</v>
+        <v>4.354147944757669e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.34423612880915e-09</v>
+        <v>4.344236128809063e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.62883812842899e-09</v>
+        <v>3.628838128428985e-09</v>
       </c>
       <c r="F3" t="n">
         <v>3.288025454157819e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>4.593357497973747e-09</v>
+        <v>4.593357497973676e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.34423612880915e-09</v>
+        <v>4.344236128809063e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.34423612880915e-09</v>
+        <v>4.344236128809063e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.308789614684682e-09</v>
+        <v>4.308789614684707e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.34423612880915e-09</v>
+        <v>4.344236128809063e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.34423612880915e-09</v>
+        <v>4.344236128809063e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.280194252047311e-09</v>
+        <v>4.280194252047327e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.412937979012951e-09</v>
+        <v>3.412937979012825e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>3.668866796882607e-09</v>
+        <v>3.66886679688231e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.606132459517592e-09</v>
+        <v>3.606132459517513e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.906714838516713e-09</v>
+        <v>2.906714838516582e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.34423612880915e-09</v>
+        <v>4.344236128809063e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.34423612880915e-09</v>
+        <v>4.344236128809063e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.34423612880915e-09</v>
+        <v>4.344236128809063e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>3.75802448916979e-09</v>
+        <v>3.758024489169771e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>3.935946552826208e-09</v>
+        <v>3.935946552826202e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.344472241342002e-09</v>
+        <v>4.344472241341769e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.016826973440476e-09</v>
+        <v>3.016826973440457e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.539090010919615e-09</v>
+        <v>5.539090010919425e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.120503528759434e-09</v>
+        <v>3.120503528759387e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.34423612880915e-09</v>
+        <v>4.344236128809063e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.545454758580955e-09</v>
+        <v>5.545454758580998e-09</v>
       </c>
     </row>
     <row r="4">
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.444419948433871e-08</v>
+        <v>3.44441994843386e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.38956302520041e-08</v>
+        <v>3.389563025200409e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.405615980412873e-08</v>
+        <v>3.405615980412857e-08</v>
       </c>
       <c r="E4" t="n">
         <v>3.480574985286113e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.431818884575439e-08</v>
+        <v>3.431818884575436e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.380055827971244e-08</v>
+        <v>3.38005582797123e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.352294578094095e-08</v>
+        <v>3.352294578094081e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.363267241289918e-08</v>
+        <v>3.363267241289905e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25403442120483e-08</v>
+        <v>3.254034421204821e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.342503981911115e-08</v>
+        <v>3.342503981911091e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>3.437877270054995e-08</v>
+        <v>3.437877270054982e-08</v>
       </c>
       <c r="M4" t="n">
         <v>3.32190450515891e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.379171921617827e-08</v>
+        <v>3.379171921617814e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.568438815403615e-08</v>
+        <v>3.568438815403604e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.429941539305966e-08</v>
+        <v>3.429941539305953e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.329863387410366e-08</v>
+        <v>3.329863387410352e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.622703152105185e-08</v>
+        <v>3.622703152105172e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.405567238474748e-08</v>
+        <v>3.405567238474727e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.32624339456532e-08</v>
+        <v>3.326243394565305e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.332202026034465e-08</v>
+        <v>3.332202026034444e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.487291889794917e-08</v>
+        <v>2.487291889794922e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.645075600894388e-08</v>
+        <v>3.645075600894376e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.6037352922257e-08</v>
+        <v>3.603735292225677e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.384741340635063e-08</v>
+        <v>3.384741340635047e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.445895931864146e-08</v>
+        <v>3.445895931864132e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.41342617831003e-08</v>
+        <v>3.413426178310013e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.320772986290143e-08</v>
+        <v>3.320772986290129e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5638,85 +5638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.304680142179142e-08</v>
+        <v>3.304680142179134e-08</v>
       </c>
       <c r="C5" t="n">
         <v>3.349461514784847e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.348470333189993e-08</v>
+        <v>3.348470333189989e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.317585389537913e-08</v>
+        <v>3.317585389537911e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.307305991094703e-08</v>
+        <v>3.307305991094698e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.357550514562957e-08</v>
+        <v>3.357550514562961e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.348470333189993e-08</v>
+        <v>3.348470333189989e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.348470333189993e-08</v>
+        <v>3.348470333189989e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.185178686318139e-08</v>
+        <v>3.18517868631813e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.348470333189993e-08</v>
+        <v>3.348470333189989e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.348470333189993e-08</v>
+        <v>3.348470333189989e-08</v>
       </c>
       <c r="M5" t="n">
         <v>3.342066145513821e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.314525609215416e-08</v>
+        <v>3.314525609215403e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.323853914099965e-08</v>
+        <v>3.323853914099962e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.321567321169418e-08</v>
+        <v>3.321567321169397e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.296074370181561e-08</v>
+        <v>3.296074370181545e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.348470333189993e-08</v>
+        <v>3.348470333189989e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.348470333189993e-08</v>
+        <v>3.348470333189989e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.348470333189993e-08</v>
+        <v>3.348470333189989e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.327103607289606e-08</v>
+        <v>3.327103607289589e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.262705254767853e-08</v>
+        <v>2.262705254767863e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.348478939214556e-08</v>
+        <v>3.34847893921455e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.300087828199341e-08</v>
+        <v>3.300087828199318e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.39202135412466e-08</v>
+        <v>3.392021354124646e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.303866716897555e-08</v>
+        <v>3.303866716897548e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.348470333189993e-08</v>
+        <v>3.348470333189989e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.388836797790586e-08</v>
+        <v>3.388836797790576e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.45219843226525e-09</v>
+        <v>3.45219843226501e-09</v>
       </c>
       <c r="C6" t="n">
         <v>2.903629199930461e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>3.064158752055219e-09</v>
+        <v>3.064158752054993e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>3.813748800787549e-09</v>
+        <v>3.813748800787548e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>3.326187793680774e-09</v>
+        <v>3.326187793680775e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>2.694928459129515e-09</v>
+        <v>2.694928459129425e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>2.530944728867408e-09</v>
+        <v>2.530944728867193e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>2.64067136082568e-09</v>
+        <v>2.640671360825437e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>3.036443638263252e-09</v>
+        <v>3.036443638263172e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>2.433038767037651e-09</v>
+        <v>2.433038767037326e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.386771648476463e-09</v>
+        <v>3.386771648476224e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>2.22704399951547e-09</v>
+        <v>2.227043999515487e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.799718164104814e-09</v>
+        <v>2.799718164104578e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>4.57875833345333e-09</v>
+        <v>4.578758333453213e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>3.193785572476807e-09</v>
+        <v>3.193785572476672e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.306632822030143e-09</v>
+        <v>2.306632822029918e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>5.235030468978362e-09</v>
+        <v>5.235030468978132e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.063671332674004e-09</v>
+        <v>3.063671332673686e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>2.270432893579664e-09</v>
+        <v>2.270432893579439e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>2.216390439761817e-09</v>
+        <v>2.21639043976164e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>4.431483011105168e-09</v>
+        <v>4.431483011105166e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>5.345126188361052e-09</v>
+        <v>5.345126188360931e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>4.931723101674186e-09</v>
+        <v>4.931723101673995e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.855412354277132e-09</v>
+        <v>2.855412354276853e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.466958266567915e-09</v>
+        <v>3.46695826656773e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.142260731026788e-09</v>
+        <v>3.142260731026515e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.215728810827845e-09</v>
+        <v>2.215728810827773e-09</v>
       </c>
     </row>
     <row r="7">
@@ -5814,85 +5814,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.054800369717809e-09</v>
+        <v>2.054800369717776e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.502614095774873e-09</v>
+        <v>2.502614095774868e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.49270227982631e-09</v>
+        <v>2.492702279826266e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.18385284330552e-09</v>
+        <v>2.183852843305518e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.081058858873374e-09</v>
+        <v>2.081058858873373e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.469875325046751e-09</v>
+        <v>2.469875325046806e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.49270227982631e-09</v>
+        <v>2.492702279826266e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.49270227982631e-09</v>
+        <v>2.492702279826266e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.347886289396347e-09</v>
+        <v>2.347886289396294e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.49270227982631e-09</v>
+        <v>2.492702279826266e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.49270227982631e-09</v>
+        <v>2.492702279826266e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.428660403064569e-09</v>
+        <v>2.428660403064588e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.153255040080689e-09</v>
+        <v>2.153255040080434e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.132909320416882e-09</v>
+        <v>2.132909320416855e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.110043391111329e-09</v>
+        <v>2.110043391111159e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.968742649741982e-09</v>
+        <v>1.968742649741869e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.49270227982631e-09</v>
+        <v>2.492702279826266e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.49270227982631e-09</v>
+        <v>2.492702279826266e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.49270227982631e-09</v>
+        <v>2.492702279826266e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.165406252313204e-09</v>
+        <v>2.165406252313048e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.185616660834601e-09</v>
+        <v>2.185616660834598e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.379159571562685e-09</v>
+        <v>2.379159571562644e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.895248461410571e-09</v>
+        <v>1.895248461410346e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.928212489173058e-09</v>
+        <v>2.928212489172822e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.046666116901853e-09</v>
+        <v>2.046666116901848e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.49270227982631e-09</v>
+        <v>2.492702279826266e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.896366925832251e-09</v>
+        <v>2.896366925832163e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6058,85 +6058,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.787235192374499e-09</v>
+        <v>5.787235192374965e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>4.65213175456656e-09</v>
+        <v>4.652131754567113e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.120009102044447e-08</v>
+        <v>1.120009102044505e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>4.23211901689723e-09</v>
+        <v>4.23211901689753e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>8.906770578155258e-09</v>
+        <v>8.90677057815526e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>4.654931865418858e-08</v>
+        <v>4.654931865418913e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.180522533596745e-09</v>
+        <v>7.180522533597253e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>1.608930635242322e-08</v>
+        <v>1.608930635242366e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.276777357344105e-08</v>
+        <v>2.276777357344126e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.535540380293464e-08</v>
+        <v>2.535540380293511e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>6.115158917500542e-08</v>
+        <v>6.11515891750059e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.620867974081827e-08</v>
+        <v>1.620867974081828e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.137658950866039e-08</v>
+        <v>2.137658950866084e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>8.124004289136793e-09</v>
+        <v>8.124004289137246e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.132257716111633e-08</v>
+        <v>1.132257716111663e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.991307921680246e-09</v>
+        <v>7.991307921680722e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>9.270675964880614e-09</v>
+        <v>9.270675964880257e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>8.082997518630064e-09</v>
+        <v>8.082997518630555e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.186760315801662e-08</v>
+        <v>1.186760315801713e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.001258506877317e-08</v>
+        <v>1.001258506877386e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>5.055397350635664e-09</v>
+        <v>5.055397350635724e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>8.533072749135016e-09</v>
+        <v>8.533072749135618e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>2.519446866771983e-08</v>
+        <v>2.519446866772045e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.447264119462146e-09</v>
+        <v>8.447264119462606e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.482206357706902e-09</v>
+        <v>9.482206357707297e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.197776479237607e-08</v>
+        <v>1.197776479237651e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.520025965349142e-08</v>
+        <v>1.520025965349141e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.647495920340499e-09</v>
+        <v>3.647495920341217e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>4.950532937492635e-09</v>
+        <v>4.950532937492679e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9708264079334e-09</v>
+        <v>4.970826407933855e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.139658235950453e-09</v>
+        <v>4.139658235950691e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.778374221833753e-09</v>
+        <v>3.778374221833751e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.245227605238742e-09</v>
+        <v>5.245227605238878e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9708264079334e-09</v>
+        <v>4.970826407933855e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9708264079334e-09</v>
+        <v>4.970826407933855e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.911934241540631e-09</v>
+        <v>4.911934241540735e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9708264079334e-09</v>
+        <v>4.970826407933855e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.9708264079334e-09</v>
+        <v>4.970826407933855e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.905904563687734e-09</v>
+        <v>4.90590456368773e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.945023891623895e-09</v>
+        <v>3.945023891624324e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.226923329960916e-09</v>
+        <v>4.226923329961091e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>4.157822965982972e-09</v>
+        <v>4.157822965983589e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.387431275949293e-09</v>
+        <v>3.387431275949396e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.9708264079334e-09</v>
+        <v>4.970826407933855e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.9708264079334e-09</v>
+        <v>4.970826407933855e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.9708264079334e-09</v>
+        <v>4.970826407933855e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.3243407151459e-09</v>
+        <v>4.324340715145927e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.470629462753674e-09</v>
+        <v>4.470629462753797e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.971086480183672e-09</v>
+        <v>4.971086480184448e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.508717144592036e-09</v>
+        <v>3.508717144592795e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.285581753238567e-09</v>
+        <v>6.285581753238887e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.622914377092682e-09</v>
+        <v>3.62291437709281e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.9708264079334e-09</v>
+        <v>4.970826407933855e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.296769652675715e-09</v>
+        <v>6.296769652675724e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.686081855441593e-08</v>
+        <v>3.68608185544169e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.643418994162942e-08</v>
+        <v>3.643418994163009e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.88337409427852e-08</v>
+        <v>3.883374094278639e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.621358330266331e-08</v>
+        <v>3.621358330266375e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.795001053386066e-08</v>
+        <v>3.795001053386085e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.17181193236971e-08</v>
+        <v>5.171811932369785e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.736865542948546e-08</v>
+        <v>3.736865542948634e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.061580251922654e-08</v>
+        <v>4.061580251922762e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.075098348835728e-08</v>
+        <v>4.075098348835737e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.399318623192814e-08</v>
+        <v>4.399318623192898e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.704047546001717e-08</v>
+        <v>5.704047546001806e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>4.061805412317461e-08</v>
+        <v>4.06180541231751e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>4.254295514326157e-08</v>
+        <v>4.254295514326233e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.77125434504577e-08</v>
+        <v>3.771254345045855e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.887838570275539e-08</v>
+        <v>3.887838570275606e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.766417718271933e-08</v>
+        <v>3.766417718272011e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.813049181136774e-08</v>
+        <v>3.813049181136856e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.769759696413386e-08</v>
+        <v>3.769759696413462e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.907704127860707e-08</v>
+        <v>3.907704127860795e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.840090896779995e-08</v>
+        <v>3.840090896780088e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.14175355921678e-08</v>
+        <v>2.141753559216776e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.786164410060264e-08</v>
+        <v>3.786164410060383e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>4.393452726493821e-08</v>
+        <v>4.393452726493908e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.783036786270273e-08</v>
+        <v>3.783036786270375e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.820759215563755e-08</v>
+        <v>3.820759215563857e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.91171939007479e-08</v>
+        <v>3.911719390074889e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.025592140556623e-08</v>
+        <v>4.025592140556653e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.608090871584662e-08</v>
+        <v>3.608090871584784e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.654295366880248e-08</v>
+        <v>3.654295366880287e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.656324713924323e-08</v>
+        <v>3.656324713924392e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.617988243373749e-08</v>
+        <v>3.617988243373825e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.608077028265175e-08</v>
+        <v>3.608077028265194e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.666326315347942e-08</v>
+        <v>3.666326315348022e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.656324713924323e-08</v>
+        <v>3.656324713924392e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.656324713924323e-08</v>
+        <v>3.656324713924392e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4242739725731e-08</v>
+        <v>3.424273972573187e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.656324713924323e-08</v>
+        <v>3.656324713924392e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.656324713924323e-08</v>
+        <v>3.656324713924392e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.64983252949976e-08</v>
+        <v>3.649832529499785e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.618935416762969e-08</v>
+        <v>3.618935416763037e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.629210320267323e-08</v>
+        <v>3.629210320267339e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.626691693142069e-08</v>
+        <v>3.626691693142119e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.59861182067993e-08</v>
+        <v>3.598611820680023e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.656324713924323e-08</v>
+        <v>3.656324713924392e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.656324713924323e-08</v>
+        <v>3.656324713924392e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.656324713924323e-08</v>
+        <v>3.656324713924392e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.632761069564055e-08</v>
+        <v>3.632761069564155e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.120439456372607e-08</v>
+        <v>2.12043945637262e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.656334193252445e-08</v>
+        <v>3.656334193252526e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.603032548170919e-08</v>
+        <v>3.603032548171032e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.704246002397025e-08</v>
+        <v>3.704246002397041e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.607194903198403e-08</v>
+        <v>3.607194903198504e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.656324713924323e-08</v>
+        <v>3.656324713924392e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.701070385032687e-08</v>
+        <v>3.701070385032732e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.222776297615515e-09</v>
+        <v>3.22277629761614e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>2.79614768482921e-09</v>
+        <v>2.796147684829284e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>5.195698685984826e-09</v>
+        <v>5.195698685985519e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>2.575541045862866e-09</v>
+        <v>2.57554104586309e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>4.311968277060123e-09</v>
+        <v>4.311968277060119e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.796111922711861e-08</v>
+        <v>1.796111922711912e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.730613172685095e-09</v>
+        <v>3.730613172685638e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>6.977760262426122e-09</v>
+        <v>6.977760262426661e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>9.260039096173705e-09</v>
+        <v>9.26003909617411e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.035514397512776e-08</v>
+        <v>1.035514397512821e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.340243320321692e-08</v>
+        <v>2.340243320321736e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.980011866374205e-09</v>
+        <v>6.980011866374201e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>8.904912886461109e-09</v>
+        <v>8.904912886461645e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.955543353879247e-09</v>
+        <v>3.955543353879839e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>5.121385606176803e-09</v>
+        <v>5.12138560617705e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.026134925918833e-09</v>
+        <v>4.026134925919394e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>4.492449554567317e-09</v>
+        <v>4.492449554567984e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>4.059554707333452e-09</v>
+        <v>4.059554707333965e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>5.438999021806703e-09</v>
+        <v>5.43899902180724e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.643908871221453e-09</v>
+        <v>4.643908871221874e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>2.755986895574333e-09</v>
+        <v>2.755986895574276e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>4.104644004024213e-09</v>
+        <v>4.104644004025016e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.017752716835966e-08</v>
+        <v>1.01775271683603e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.192325605902346e-09</v>
+        <v>4.192325605902882e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.569549898837176e-09</v>
+        <v>4.569549898837737e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.479151643947492e-09</v>
+        <v>5.479151643948047e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.61787914876576e-09</v>
+        <v>6.617879148765761e-09</v>
       </c>
     </row>
     <row r="7">
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.442866459046233e-09</v>
+        <v>2.442866459046914e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.904911412001977e-09</v>
+        <v>2.904911412002052e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.925204882442771e-09</v>
+        <v>2.925204882443263e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.54184017693706e-09</v>
+        <v>2.54184017693727e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.442728025851364e-09</v>
+        <v>2.442728025851365e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.906263056900914e-09</v>
+        <v>2.906263056901476e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.925204882442771e-09</v>
+        <v>2.925204882443263e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.925204882442771e-09</v>
+        <v>2.925204882443263e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.751795333547417e-09</v>
+        <v>2.751795333547695e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.925204882442771e-09</v>
+        <v>2.925204882443263e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.925204882442771e-09</v>
+        <v>2.925204882443263e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.860283038197189e-09</v>
+        <v>2.86028303819719e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.551311910829296e-09</v>
+        <v>2.55131191082963e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.535103106094652e-09</v>
+        <v>2.535103106094696e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.509916834842117e-09</v>
+        <v>2.509916834842366e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.34807594999894e-09</v>
+        <v>2.348075949999468e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.925204882442771e-09</v>
+        <v>2.925204882443263e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.925204882442771e-09</v>
+        <v>2.925204882443263e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.925204882442771e-09</v>
+        <v>2.925204882443263e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.570610599061937e-09</v>
+        <v>2.570610599062535e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.542845867132635e-09</v>
+        <v>2.542845867132557e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.806341835946012e-09</v>
+        <v>2.806341835946603e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.273325385130568e-09</v>
+        <v>2.273325385131336e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.404417767169738e-09</v>
+        <v>3.404417767169755e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.4339067751835e-09</v>
+        <v>2.433906775184145e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.925204882442771e-09</v>
+        <v>2.925204882443263e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.372661593526537e-09</v>
+        <v>3.372661593526541e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6742,82 +6742,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.753461369731984e-09</v>
+        <v>3.753461369732036e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>5.03388718395735e-09</v>
+        <v>5.033887183957344e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>5.21752351291221e-09</v>
+        <v>5.217523512912257e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>5.100050497081546e-09</v>
+        <v>5.100050497081551e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>6.33067697348929e-09</v>
+        <v>6.330676973489284e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>3.578463737907401e-08</v>
+        <v>3.578463737907408e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>4.345713867417085e-09</v>
+        <v>4.345713867417124e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>6.029541108260136e-09</v>
+        <v>6.029541108260181e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.746982560466028e-08</v>
+        <v>1.746982560466026e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>7.920039695981673e-09</v>
+        <v>7.920039695981719e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>2.491084823891253e-08</v>
+        <v>2.491084823891257e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>5.637882186498558e-09</v>
+        <v>5.63788218649856e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>5.400667174283523e-09</v>
+        <v>5.400667174283554e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>4.437154913946838e-09</v>
+        <v>4.437154913946891e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.122315623464666e-08</v>
+        <v>1.122315623464669e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.46103982443568e-09</v>
+        <v>6.461039824435726e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>9.786389529624804e-09</v>
+        <v>9.786389529624854e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>7.360277041472995e-09</v>
+        <v>7.360277041473049e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>5.379598450187524e-09</v>
+        <v>5.379598450187539e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>4.822965935091116e-09</v>
+        <v>4.822965935091186e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>5.308852372773049e-09</v>
+        <v>5.308852372773048e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.001822304289203e-08</v>
+        <v>1.001822304289207e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.721572261352195e-08</v>
+        <v>1.7215722613522e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.280213181716857e-08</v>
+        <v>1.280213181716859e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.120071840785738e-09</v>
+        <v>5.120071840785788e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.899116306950169e-09</v>
+        <v>5.899116306950212e-09</v>
       </c>
       <c r="AB2" t="n">
         <v>3.075842422686626e-07</v>
@@ -6830,85 +6830,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.45890312432018e-09</v>
+        <v>3.458903124320227e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>4.736397404775939e-09</v>
+        <v>4.736397404775923e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.73804244466933e-09</v>
+        <v>4.738042444669376e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.955403411723941e-09</v>
+        <v>3.955403411723942e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.596056552617855e-09</v>
+        <v>3.596056552617857e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.003280315568545e-09</v>
+        <v>5.003280315568596e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.73804244466933e-09</v>
+        <v>4.738042444669376e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.73804244466933e-09</v>
+        <v>4.738042444669376e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.692804736340769e-09</v>
+        <v>4.692804736340788e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.73804244466933e-09</v>
+        <v>4.738042444669376e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.73804244466933e-09</v>
+        <v>4.738042444669376e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.664153564433277e-09</v>
+        <v>4.664153564433281e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.746495475996733e-09</v>
+        <v>3.746495475996769e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.01898119241108e-09</v>
+        <v>4.018981192411118e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.952188359143735e-09</v>
+        <v>3.952188359143808e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.207523052905317e-09</v>
+        <v>3.207523052905383e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.73804244466933e-09</v>
+        <v>4.738042444669376e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.73804244466933e-09</v>
+        <v>4.738042444669376e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.73804244466933e-09</v>
+        <v>4.738042444669376e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.113268005267329e-09</v>
+        <v>4.113268005267359e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.275815639073607e-09</v>
+        <v>4.275815639073609e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.738293832096302e-09</v>
+        <v>4.738293832096358e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.32475871326516e-09</v>
+        <v>3.324758713265188e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.009102668952995e-09</v>
+        <v>6.009102668953041e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.435142454691603e-09</v>
+        <v>3.435142454691649e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.73804244466933e-09</v>
+        <v>4.738042444669376e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.063961951313755e-09</v>
+        <v>7.063961951313765e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6918,82 +6918,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.484631531062663e-08</v>
+        <v>3.48463153106267e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.531197004222345e-08</v>
+        <v>3.531197004222346e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.537994876993017e-08</v>
+        <v>3.537994876993023e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.527260450131718e-08</v>
+        <v>3.52726045013172e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.574620117439752e-08</v>
+        <v>3.574620117439754e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.652130283697315e-08</v>
+        <v>4.652130283697321e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.506218439145293e-08</v>
+        <v>3.506218439145298e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.567591964824243e-08</v>
+        <v>3.567591964824253e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.786580862034096e-08</v>
+        <v>3.7865808620341e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.636498418411173e-08</v>
+        <v>3.636498418411179e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.255793438186302e-08</v>
+        <v>4.255793438186311e-08</v>
       </c>
       <c r="M4" t="n">
         <v>3.548620731931477e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.544670248391858e-08</v>
+        <v>3.544670248391865e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.509551357915804e-08</v>
+        <v>3.509551357915812e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.756893137530242e-08</v>
+        <v>3.75689313753025e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.58331958633747e-08</v>
+        <v>3.583319586337477e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.704524678268848e-08</v>
+        <v>3.704524678268856e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.616095726960828e-08</v>
+        <v>3.616095726960836e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.543902318138699e-08</v>
+        <v>3.543902318138708e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.523613716594336e-08</v>
+        <v>3.523613716594346e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>2.232399217125047e-08</v>
+        <v>2.232399217125039e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.712974737594778e-08</v>
+        <v>3.712974737594783e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.975315145213535e-08</v>
+        <v>3.975315145213542e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.814444943386429e-08</v>
+        <v>3.814444943386437e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.534442877977539e-08</v>
+        <v>3.534442877977545e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.562838133969033e-08</v>
+        <v>3.562838133969041e-08</v>
       </c>
       <c r="AB4" t="n">
         <v>1.462180659045635e-07</v>
@@ -7006,85 +7006,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.473895228905166e-08</v>
+        <v>3.473895228905171e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.520353851101323e-08</v>
+        <v>3.520353851101324e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.520518355090658e-08</v>
+        <v>3.520518355090662e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4855394079829e-08</v>
+        <v>3.485539407982903e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.474946414252406e-08</v>
+        <v>3.474946414252411e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.530185964026909e-08</v>
+        <v>3.530185964026912e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.520518355090658e-08</v>
+        <v>3.520518355090662e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.520518355090658e-08</v>
+        <v>3.520518355090662e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.320873454919247e-08</v>
+        <v>3.320873454919254e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.520518355090658e-08</v>
+        <v>3.520518355090662e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.520518355090658e-08</v>
+        <v>3.520518355090662e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.51312946706707e-08</v>
+        <v>3.513129467067071e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.484377632415782e-08</v>
+        <v>3.484377632415785e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.494309416810205e-08</v>
+        <v>3.494309416810207e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.491874896469711e-08</v>
+        <v>3.491874896469717e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.464732720487472e-08</v>
+        <v>3.464732720487478e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.520518355090658e-08</v>
+        <v>3.520518355090662e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.520518355090658e-08</v>
+        <v>3.520518355090662e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.520518355090658e-08</v>
+        <v>3.520518355090662e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.497746060421644e-08</v>
+        <v>3.497746060421649e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>2.19474624123469e-08</v>
+        <v>2.194746241234671e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.520527517867182e-08</v>
+        <v>3.520527517867189e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.469005822642522e-08</v>
+        <v>3.469005822642529e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.566847007711529e-08</v>
+        <v>3.566847007711535e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.473029180398392e-08</v>
+        <v>3.473029180398396e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.520518355090658e-08</v>
+        <v>3.520518355090662e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.668195261618679e-08</v>
+        <v>3.668195261618681e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7094,82 +7094,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.403651268374043e-09</v>
+        <v>2.403651268374093e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>2.869305999970902e-09</v>
+        <v>2.869305999970904e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.937284727677579e-09</v>
+        <v>2.937284727677613e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>2.829940459064574e-09</v>
+        <v>2.829940459064575e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>3.30353713214491e-09</v>
+        <v>3.303537132144908e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.39618661144145e-08</v>
+        <v>1.396186611441456e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.619520349200326e-09</v>
+        <v>2.619520349200344e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>3.233255605989879e-09</v>
+        <v>3.233255605989922e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>7.261933335939909e-09</v>
+        <v>7.261933335939934e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>3.922320141859165e-09</v>
+        <v>3.922320141859205e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.011527033961044e-08</v>
+        <v>1.011527033961049e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.043543277062154e-09</v>
+        <v>3.043543277062156e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.004038441665979e-09</v>
+        <v>3.004038441666036e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>2.536076856599375e-09</v>
+        <v>2.536076856599427e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>5.009494652743815e-09</v>
+        <v>5.009494652743867e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.390531821122126e-09</v>
+        <v>3.390531821122164e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>4.60258274043586e-09</v>
+        <v>4.602582740435893e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7182932273557e-09</v>
+        <v>3.718293227355744e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>2.996359139134409e-09</v>
+        <v>2.996359139134477e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>2.676700443384716e-09</v>
+        <v>2.676700443384787e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>2.788928276852702e-09</v>
+        <v>2.788928276852703e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>4.570310653389143e-09</v>
+        <v>4.570310653389199e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>7.193714729576696e-09</v>
+        <v>7.193714729576745e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.701785391611711e-09</v>
+        <v>5.701785391611769e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.901764737522791e-09</v>
+        <v>2.901764737522825e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.185717297437734e-09</v>
+        <v>3.185717297437774e-09</v>
       </c>
       <c r="AB6" t="n">
         <v>1.137754018623107e-07</v>
@@ -7182,13 +7182,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.296288246799024e-09</v>
+        <v>2.296288246799034e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.760874468760633e-09</v>
+        <v>2.760874468760642e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.76251950865405e-09</v>
+        <v>2.762519508654057e-09</v>
       </c>
       <c r="E7" t="n">
         <v>2.412730037576418e-09</v>
@@ -7197,70 +7197,70 @@
         <v>2.306800100271493e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.742422917710399e-09</v>
+        <v>2.742422917710436e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.76251950865405e-09</v>
+        <v>2.762519508654057e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.76251950865405e-09</v>
+        <v>2.762519508654057e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.604859264791459e-09</v>
+        <v>2.604859264791478e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.76251950865405e-09</v>
+        <v>2.762519508654057e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.76251950865405e-09</v>
+        <v>2.762519508654057e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.688630628418124e-09</v>
+        <v>2.688630628418126e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.401112281905247e-09</v>
+        <v>2.401112281905236e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.383657445543362e-09</v>
+        <v>2.383657445543396e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>2.359312242138467e-09</v>
+        <v>2.359312242138504e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.204663162622141e-09</v>
+        <v>2.204663162622155e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.76251950865405e-09</v>
+        <v>2.762519508654057e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.76251950865405e-09</v>
+        <v>2.762519508654057e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.76251950865405e-09</v>
+        <v>2.762519508654057e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.418023881657812e-09</v>
+        <v>2.418023881657839e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.412398517949025e-09</v>
+        <v>2.412398517949028e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.645838456113164e-09</v>
+        <v>2.645838456113199e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>2.130621503866571e-09</v>
+        <v>2.130621503866635e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.225806034862745e-09</v>
+        <v>3.22580603486274e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.287627761731263e-09</v>
+        <v>2.28762776173129e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.76251950865405e-09</v>
+        <v>2.762519508654057e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.239288573934211e-09</v>
+        <v>4.239288573934212e-09</v>
       </c>
     </row>
   </sheetData>
